--- a/template/Template_perizinan Proyek.xlsx
+++ b/template/Template_perizinan Proyek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvin\Documents\Coolyeah\PKT\Inventor\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D6A335-39E6-42D4-AC4E-AC2A88208676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E388ECFA-940D-4351-BCB4-FD672D552450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,310 +20,520 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="99">
-  <si>
-    <t>Nama Proyek</t>
-  </si>
-  <si>
-    <t>Jenis Proyek</t>
-  </si>
-  <si>
-    <t>Nomor Seri proyek</t>
-  </si>
-  <si>
-    <t>Lokasi</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="169">
   <si>
     <t>Penanggung Jawab</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Keterangan Kolom Perizinan proyek</t>
-  </si>
-  <si>
-    <t>Pembangunan Gudang Bahan Baku</t>
-  </si>
-  <si>
-    <t>Infrastruktur</t>
-  </si>
-  <si>
-    <t>PRJ-001</t>
-  </si>
-  <si>
-    <t>Bontang</t>
-  </si>
-  <si>
-    <t>Departemen Operasional</t>
-  </si>
-  <si>
     <t>Aktif</t>
   </si>
   <si>
-    <t>Keterangan Kolom proyek</t>
-  </si>
-  <si>
-    <t>Revitalisasi Area Produksi A</t>
-  </si>
-  <si>
-    <t>Revitalisasi</t>
-  </si>
-  <si>
-    <t>PRJ-002</t>
-  </si>
-  <si>
-    <t>Departemen Engineering</t>
-  </si>
-  <si>
-    <t>Nama proyek</t>
-  </si>
-  <si>
-    <t>Pemasangan Sistem CCTV</t>
-  </si>
-  <si>
-    <t>Keamanan</t>
-  </si>
-  <si>
-    <t>PRJ-003</t>
-  </si>
-  <si>
-    <t>Gudang Utama</t>
-  </si>
-  <si>
-    <t>Departemen Logistik</t>
-  </si>
-  <si>
-    <t>Departemen IT</t>
-  </si>
-  <si>
-    <t>Selesai</t>
-  </si>
-  <si>
-    <t>Nama atau identitas utama proyek yang digunakan untuk membedakan setiap proyek.</t>
-  </si>
-  <si>
-    <t>Modernisasi Panel Listrik</t>
-  </si>
-  <si>
-    <t>Kelistrikan</t>
-  </si>
-  <si>
-    <t>PRJ-004</t>
-  </si>
-  <si>
-    <t>Area Utility</t>
-  </si>
-  <si>
-    <t>Jenis proyek</t>
-  </si>
-  <si>
-    <t>Pengembangan Sistem Inventaris</t>
-  </si>
-  <si>
-    <t>Teknologi Informasi</t>
-  </si>
-  <si>
-    <t>PRJ-005</t>
-  </si>
-  <si>
-    <t>Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Kategori atau klasifikasi proyek sesuai jenisnya.</t>
-  </si>
-  <si>
-    <t>Renovasi Ruang Kontrol</t>
-  </si>
-  <si>
-    <t>Renovasi</t>
-  </si>
-  <si>
-    <t>PRJ-006</t>
-  </si>
-  <si>
-    <t>Control Room</t>
-  </si>
-  <si>
-    <t>Departemen General Affair</t>
-  </si>
-  <si>
-    <t>Instalasi Jaringan Fiber Optik</t>
-  </si>
-  <si>
-    <t>Infrastruktur Jaringan</t>
-  </si>
-  <si>
-    <t>PRJ-007</t>
-  </si>
-  <si>
-    <t>Area Produksi</t>
-  </si>
-  <si>
-    <t>Nomor seri (Serial Number) yang menjadi identitas unik setiap proyek. Apabila proyek tidak memiliki nomor seri, kolom dapat dikosongkan atau diisi dengan tanda "-".</t>
-  </si>
-  <si>
-    <t>Pembangunan Pos Keamanan</t>
-  </si>
-  <si>
-    <t>Konstruksi</t>
-  </si>
-  <si>
-    <t>PRJ-008</t>
-  </si>
-  <si>
-    <t>Gerbang Utama</t>
-  </si>
-  <si>
-    <t>Departemen Security</t>
-  </si>
-  <si>
-    <t>Peningkatan Kapasitas Server</t>
-  </si>
-  <si>
-    <t>PRJ-009</t>
-  </si>
-  <si>
-    <t>Data Center</t>
-  </si>
-  <si>
-    <t>Lokasi atau area tempat proyek berada atau digunakan.</t>
-  </si>
-  <si>
-    <t>Perbaikan Drainase Kawasan</t>
-  </si>
-  <si>
-    <t>PRJ-010</t>
-  </si>
-  <si>
-    <t>Area Barat</t>
-  </si>
-  <si>
-    <t>Departemen Facility</t>
-  </si>
-  <si>
-    <t>Ditunda</t>
-  </si>
-  <si>
-    <t>Pemasangan Sistem Fire Alarm</t>
-  </si>
-  <si>
-    <t>Keselamatan</t>
-  </si>
-  <si>
-    <t>PRJ-011</t>
-  </si>
-  <si>
-    <t>Gedung Administrasi</t>
-  </si>
-  <si>
-    <t>Departemen HSE</t>
-  </si>
-  <si>
-    <t>Unit, departemen, atau pihak yang memiliki dan bertanggung jawab atas pengelolaan proyek.</t>
-  </si>
-  <si>
-    <t>Pengembangan Area Parkir</t>
-  </si>
-  <si>
-    <t>PRJ-012</t>
-  </si>
-  <si>
-    <t>Area Selatan</t>
-  </si>
-  <si>
-    <t>Upgrade Sistem HVAC</t>
-  </si>
-  <si>
-    <t>Mekanikal</t>
-  </si>
-  <si>
-    <t>PRJ-013</t>
-  </si>
-  <si>
-    <t>Gedung Produksi</t>
-  </si>
-  <si>
-    <t>Kondisi atau status operasional proyek. Pilihan yang tersedia hanya:</t>
-  </si>
-  <si>
-    <t>Pembangunan Ruang Arsip</t>
-  </si>
-  <si>
-    <t>PRJ-014</t>
-  </si>
-  <si>
-    <t>Kantor Administrasi</t>
-  </si>
-  <si>
-    <t>Implementasi Sistem Absensi Digital</t>
-  </si>
-  <si>
-    <t>PRJ-015</t>
-  </si>
-  <si>
-    <t>Departemen HR</t>
-  </si>
-  <si>
-    <t>Peningkatan Sistem Penerangan</t>
-  </si>
-  <si>
-    <t>PRJ-016</t>
-  </si>
-  <si>
-    <t>Renovasi Laboratorium QC</t>
-  </si>
-  <si>
-    <t>PRJ-017</t>
-  </si>
-  <si>
-    <t>Laboratorium QC</t>
-  </si>
-  <si>
-    <t>Departemen Quality Control</t>
-  </si>
-  <si>
-    <t>Pembangunan Jalur Evakuasi</t>
-  </si>
-  <si>
-    <t>PRJ-018</t>
-  </si>
-  <si>
-    <t>Catatan Pengisian Data</t>
-  </si>
-  <si>
-    <t>Integrasi Sistem Monitoring Produksi</t>
-  </si>
-  <si>
-    <t>Otomasi Industri</t>
-  </si>
-  <si>
-    <t>PRJ-019</t>
-  </si>
-  <si>
-    <t>Kolom Nama proyek, Lokasi, dan Status merupakan kolom wajib diisi. Ketiga kolom tersebut digunakan sebagai informasi utama untuk mengidentifikasi proyek beserta kondisi operasionalnya.</t>
-  </si>
-  <si>
-    <t>Pengembangan Gudang Penyimpanan</t>
-  </si>
-  <si>
-    <t>PRJ-020</t>
-  </si>
-  <si>
-    <t>Gudang Logistik</t>
-  </si>
-  <si>
-    <t>Kolom Jenis proyek, Nomor Seri Produk, dan Penanggung Jawab bersifat opsional. Apabila data belum tersedia, kolom dapat dikosongkan atau diisi dengan tanda "-". Data tersebut dapat diperbarui sewaktu-waktu setelah informasi tersedia.</t>
-  </si>
-  <si>
-    <t>Penulisan Status hanya diperbolehkan menggunakan salah satu nilai berikut: Aktif, Spare, atau Rusak, agar sistem dapat memproses data dengan benar.</t>
+    <t>Status Aset</t>
+  </si>
+  <si>
+    <t>Nama Sertifikat (Child)</t>
+  </si>
+  <si>
+    <t>No Sertifikat Active</t>
+  </si>
+  <si>
+    <t>Tgl Terbit</t>
+  </si>
+  <si>
+    <t>Tgl Expired</t>
+  </si>
+  <si>
+    <t>Overhead Crane 1 Ton</t>
+  </si>
+  <si>
+    <t>Aset Peralatan</t>
+  </si>
+  <si>
+    <t>CR-001</t>
+  </si>
+  <si>
+    <t>Bay 1</t>
+  </si>
+  <si>
+    <t>Dept Pemeliharaan</t>
+  </si>
+  <si>
+    <t>Sertifikat Layak Operasi</t>
+  </si>
+  <si>
+    <t>SLO-CR001</t>
+  </si>
+  <si>
+    <t>Sertifikat K3</t>
+  </si>
+  <si>
+    <t>K3-CR001</t>
+  </si>
+  <si>
+    <t>Overhead Crane 2 Ton</t>
+  </si>
+  <si>
+    <t>CR-002</t>
+  </si>
+  <si>
+    <t>Bay 2</t>
+  </si>
+  <si>
+    <t>SLO-CR002</t>
+  </si>
+  <si>
+    <t>K3-CR002</t>
+  </si>
+  <si>
+    <t>Overhead Crane 3 Ton</t>
+  </si>
+  <si>
+    <t>CR-003</t>
+  </si>
+  <si>
+    <t>Bay 3</t>
+  </si>
+  <si>
+    <t>SLO-CR003</t>
+  </si>
+  <si>
+    <t>K3-CR003</t>
+  </si>
+  <si>
+    <t>Overhead Crane 4 Ton</t>
+  </si>
+  <si>
+    <t>CR-004</t>
+  </si>
+  <si>
+    <t>Bay 4</t>
+  </si>
+  <si>
+    <t>SLO-CR004</t>
+  </si>
+  <si>
+    <t>K3-CR004</t>
+  </si>
+  <si>
+    <t>Overhead Crane 5 Ton</t>
+  </si>
+  <si>
+    <t>CR-005</t>
+  </si>
+  <si>
+    <t>Bay 5</t>
+  </si>
+  <si>
+    <t>SLO-CR005</t>
+  </si>
+  <si>
+    <t>K3-CR005</t>
+  </si>
+  <si>
+    <t>Overhead Crane 6 Ton</t>
+  </si>
+  <si>
+    <t>CR-006</t>
+  </si>
+  <si>
+    <t>Bay 6</t>
+  </si>
+  <si>
+    <t>SLO-CR006</t>
+  </si>
+  <si>
+    <t>K3-CR006</t>
+  </si>
+  <si>
+    <t>Overhead Crane 7 Ton</t>
+  </si>
+  <si>
+    <t>CR-007</t>
+  </si>
+  <si>
+    <t>Bay 7</t>
+  </si>
+  <si>
+    <t>SLO-CR007</t>
+  </si>
+  <si>
+    <t>K3-CR007</t>
+  </si>
+  <si>
+    <t>Overhead Crane 8 Ton</t>
+  </si>
+  <si>
+    <t>CR-008</t>
+  </si>
+  <si>
+    <t>Bay 8</t>
+  </si>
+  <si>
+    <t>SLO-CR008</t>
+  </si>
+  <si>
+    <t>K3-CR008</t>
+  </si>
+  <si>
+    <t>Overhead Crane 9 Ton</t>
+  </si>
+  <si>
+    <t>CR-009</t>
+  </si>
+  <si>
+    <t>Bay 9</t>
+  </si>
+  <si>
+    <t>SLO-CR009</t>
+  </si>
+  <si>
+    <t>K3-CR009</t>
+  </si>
+  <si>
+    <t>Overhead Crane 10 Ton</t>
+  </si>
+  <si>
+    <t>CR-010</t>
+  </si>
+  <si>
+    <t>Bay 10</t>
+  </si>
+  <si>
+    <t>SLO-CR010</t>
+  </si>
+  <si>
+    <t>K3-CR010</t>
+  </si>
+  <si>
+    <t>Forklift 1 Ton</t>
+  </si>
+  <si>
+    <t>Aset Kendaraan</t>
+  </si>
+  <si>
+    <t>FL-001</t>
+  </si>
+  <si>
+    <t>Gudang 1</t>
+  </si>
+  <si>
+    <t>Dept Logistik</t>
+  </si>
+  <si>
+    <t>SLO-FL001</t>
+  </si>
+  <si>
+    <t>K3-FL001</t>
+  </si>
+  <si>
+    <t>Forklift 2 Ton</t>
+  </si>
+  <si>
+    <t>FL-002</t>
+  </si>
+  <si>
+    <t>Gudang 2</t>
+  </si>
+  <si>
+    <t>SLO-FL002</t>
+  </si>
+  <si>
+    <t>K3-FL002</t>
+  </si>
+  <si>
+    <t>Forklift 3 Ton</t>
+  </si>
+  <si>
+    <t>FL-003</t>
+  </si>
+  <si>
+    <t>Gudang 3</t>
+  </si>
+  <si>
+    <t>SLO-FL003</t>
+  </si>
+  <si>
+    <t>K3-FL003</t>
+  </si>
+  <si>
+    <t>Forklift 4 Ton</t>
+  </si>
+  <si>
+    <t>FL-004</t>
+  </si>
+  <si>
+    <t>Gudang 4</t>
+  </si>
+  <si>
+    <t>SLO-FL004</t>
+  </si>
+  <si>
+    <t>K3-FL004</t>
+  </si>
+  <si>
+    <t>Forklift 5 Ton</t>
+  </si>
+  <si>
+    <t>FL-005</t>
+  </si>
+  <si>
+    <t>Gudang 5</t>
+  </si>
+  <si>
+    <t>SLO-FL005</t>
+  </si>
+  <si>
+    <t>K3-FL005</t>
+  </si>
+  <si>
+    <t>Forklift 6 Ton</t>
+  </si>
+  <si>
+    <t>FL-006</t>
+  </si>
+  <si>
+    <t>Gudang 6</t>
+  </si>
+  <si>
+    <t>SLO-FL006</t>
+  </si>
+  <si>
+    <t>K3-FL006</t>
+  </si>
+  <si>
+    <t>Forklift 7 Ton</t>
+  </si>
+  <si>
+    <t>FL-007</t>
+  </si>
+  <si>
+    <t>Gudang 7</t>
+  </si>
+  <si>
+    <t>SLO-FL007</t>
+  </si>
+  <si>
+    <t>K3-FL007</t>
+  </si>
+  <si>
+    <t>Forklift 8 Ton</t>
+  </si>
+  <si>
+    <t>FL-008</t>
+  </si>
+  <si>
+    <t>Gudang 8</t>
+  </si>
+  <si>
+    <t>SLO-FL008</t>
+  </si>
+  <si>
+    <t>K3-FL008</t>
+  </si>
+  <si>
+    <t>Forklift 9 Ton</t>
+  </si>
+  <si>
+    <t>FL-009</t>
+  </si>
+  <si>
+    <t>Gudang 9</t>
+  </si>
+  <si>
+    <t>SLO-FL009</t>
+  </si>
+  <si>
+    <t>K3-FL009</t>
+  </si>
+  <si>
+    <t>Forklift 10 Ton</t>
+  </si>
+  <si>
+    <t>FL-010</t>
+  </si>
+  <si>
+    <t>Gudang 10</t>
+  </si>
+  <si>
+    <t>SLO-FL010</t>
+  </si>
+  <si>
+    <t>K3-FL010</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 1</t>
+  </si>
+  <si>
+    <t>Mesin Produksi</t>
+  </si>
+  <si>
+    <t>KP-001</t>
+  </si>
+  <si>
+    <t>Pabrik 1</t>
+  </si>
+  <si>
+    <t>Dept Produksi</t>
+  </si>
+  <si>
+    <t>Sertifikat Tekanan Tinggi</t>
+  </si>
+  <si>
+    <t>STT-KP001</t>
+  </si>
+  <si>
+    <t>K3-KP001</t>
+  </si>
+  <si>
+    <t>KP-002</t>
+  </si>
+  <si>
+    <t>Pabrik 2</t>
+  </si>
+  <si>
+    <t>STT-KP002</t>
+  </si>
+  <si>
+    <t>K3-KP002</t>
+  </si>
+  <si>
+    <t>KP-003</t>
+  </si>
+  <si>
+    <t>Pabrik 3</t>
+  </si>
+  <si>
+    <t>STT-KP003</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 3</t>
+  </si>
+  <si>
+    <t>K3-KP003</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 4</t>
+  </si>
+  <si>
+    <t>KP-004</t>
+  </si>
+  <si>
+    <t>Pabrik 4</t>
+  </si>
+  <si>
+    <t>STT-KP004</t>
+  </si>
+  <si>
+    <t>K3-KP004</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 5</t>
+  </si>
+  <si>
+    <t>KP-005</t>
+  </si>
+  <si>
+    <t>Pabrik 5</t>
+  </si>
+  <si>
+    <t>STT-KP005</t>
+  </si>
+  <si>
+    <t>K3-KP005</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 6</t>
+  </si>
+  <si>
+    <t>KP-006</t>
+  </si>
+  <si>
+    <t>Pabrik 6</t>
+  </si>
+  <si>
+    <t>STT-KP006</t>
+  </si>
+  <si>
+    <t>K3-KP006</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 7</t>
+  </si>
+  <si>
+    <t>KP-007</t>
+  </si>
+  <si>
+    <t>Pabrik 7</t>
+  </si>
+  <si>
+    <t>STT-KP007</t>
+  </si>
+  <si>
+    <t>K3-KP007</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 8</t>
+  </si>
+  <si>
+    <t>KP-008</t>
+  </si>
+  <si>
+    <t>Pabrik 8</t>
+  </si>
+  <si>
+    <t>STT-KP008</t>
+  </si>
+  <si>
+    <t>K3-KP008</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 9</t>
+  </si>
+  <si>
+    <t>KP-009</t>
+  </si>
+  <si>
+    <t>Pabrik 9</t>
+  </si>
+  <si>
+    <t>STT-KP009</t>
+  </si>
+  <si>
+    <t>K3-KP009</t>
+  </si>
+  <si>
+    <t>Kompresor Nitrogen 10</t>
+  </si>
+  <si>
+    <t>KP-010</t>
+  </si>
+  <si>
+    <t>Pabrik 10</t>
+  </si>
+  <si>
+    <t>STT-KP010</t>
+  </si>
+  <si>
+    <t>K3-KP010</t>
+  </si>
+  <si>
+    <t>Nama Proyek / Master (Wajib)</t>
+  </si>
+  <si>
+    <t>Jenis Proyek ( master )</t>
+  </si>
+  <si>
+    <t>No Proyek</t>
+  </si>
+  <si>
+    <t>Lokasi proyek</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -331,61 +541,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="25"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="19"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -400,7 +560,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -408,90 +568,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,3641 +810,4777 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="14" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="3" t="s">
+      <c r="H2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="I2" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J2" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="H3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="I3" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J3" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="4" t="s">
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J4" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="I5" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J5" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="I6" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J6" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="5" t="s">
+      <c r="I7" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J7" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="I8" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J8" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="I9" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J9" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="4" t="s">
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J10" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="I11" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J11" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="5" t="s">
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J12" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="I13" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J13" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D14" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="I14" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J14" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="I15" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J15" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="5" t="s">
+      <c r="H16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J16" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D17" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="I17" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J17" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D18" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="I18" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J18" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J19" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="H20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="3">
+        <v>45658</v>
+      </c>
+      <c r="J20" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B21" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C21" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D21" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="I21" s="3">
+        <v>45809</v>
+      </c>
+      <c r="J21" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B22" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C22" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D22" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E22" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="5" t="s">
+      <c r="H22" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="I22" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J22" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="I23" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J23" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="D24" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="I24" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J24" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="I25" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J25" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="5" t="s">
+      <c r="H26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J26" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="D27" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="5" t="s">
+      <c r="I27" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J27" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="H28" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J28" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D29" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="E29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="I29" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J29" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="H30" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J30" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D31" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="E31" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I31" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J31" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="H32" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J32" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="F33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="I33" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J33" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="5" t="s">
+      <c r="H34" t="s">
+        <v>96</v>
+      </c>
+      <c r="I34" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J34" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D35" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="5" t="s">
+      <c r="E35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="5" t="s">
+      <c r="I35" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J35" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="8"/>
-    </row>
-    <row r="33" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="8"/>
-    </row>
-    <row r="35" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="8"/>
-    </row>
-    <row r="37" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="10"/>
-    </row>
-    <row r="41" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H51" s="6"/>
-    </row>
-    <row r="52" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H52" s="6"/>
-    </row>
-    <row r="53" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H53" s="6"/>
-    </row>
-    <row r="54" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H55" s="6"/>
-    </row>
-    <row r="56" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H56" s="6"/>
-    </row>
-    <row r="57" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H58" s="6"/>
-    </row>
-    <row r="59" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H59" s="6"/>
-    </row>
-    <row r="60" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H60" s="6"/>
-    </row>
-    <row r="61" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H61" s="6"/>
-    </row>
-    <row r="62" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H64" s="6"/>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" t="s">
+        <v>101</v>
+      </c>
+      <c r="I36" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J36" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" t="s">
+        <v>65</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s">
+        <v>102</v>
+      </c>
+      <c r="I37" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J37" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" t="s">
+        <v>106</v>
+      </c>
+      <c r="I38" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J38" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" t="s">
+        <v>107</v>
+      </c>
+      <c r="I39" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J39" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" t="s">
+        <v>65</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="3">
+        <v>45689</v>
+      </c>
+      <c r="J40" s="3">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>112</v>
+      </c>
+      <c r="I41" s="3">
+        <v>45839</v>
+      </c>
+      <c r="J41" s="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42" t="s">
+        <v>117</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>118</v>
+      </c>
+      <c r="H42" t="s">
+        <v>119</v>
+      </c>
+      <c r="I42" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J42" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43" t="s">
+        <v>117</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>120</v>
+      </c>
+      <c r="I43" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J43" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" t="s">
+        <v>117</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" t="s">
+        <v>123</v>
+      </c>
+      <c r="I44" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J44" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45" t="s">
+        <v>117</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s">
+        <v>124</v>
+      </c>
+      <c r="I45" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J45" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" t="s">
+        <v>117</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>118</v>
+      </c>
+      <c r="H46" t="s">
+        <v>127</v>
+      </c>
+      <c r="I46" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J46" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" t="s">
+        <v>117</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s">
+        <v>129</v>
+      </c>
+      <c r="I47" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J47" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" t="s">
+        <v>131</v>
+      </c>
+      <c r="D48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E48" t="s">
+        <v>117</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>118</v>
+      </c>
+      <c r="H48" t="s">
+        <v>133</v>
+      </c>
+      <c r="I48" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J48" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" t="s">
+        <v>132</v>
+      </c>
+      <c r="E49" t="s">
+        <v>117</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J49" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>135</v>
+      </c>
+      <c r="B50" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" t="s">
+        <v>117</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>118</v>
+      </c>
+      <c r="H50" t="s">
+        <v>138</v>
+      </c>
+      <c r="I50" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J50" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" t="s">
+        <v>117</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s">
+        <v>139</v>
+      </c>
+      <c r="I51" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J51" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>140</v>
+      </c>
+      <c r="B52" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" t="s">
+        <v>142</v>
+      </c>
+      <c r="E52" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>118</v>
+      </c>
+      <c r="H52" t="s">
+        <v>143</v>
+      </c>
+      <c r="I52" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J52" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" t="s">
+        <v>117</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s">
+        <v>144</v>
+      </c>
+      <c r="I53" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J53" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>145</v>
+      </c>
+      <c r="B54" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" t="s">
+        <v>146</v>
+      </c>
+      <c r="D54" t="s">
+        <v>147</v>
+      </c>
+      <c r="E54" t="s">
+        <v>117</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>118</v>
+      </c>
+      <c r="H54" t="s">
+        <v>148</v>
+      </c>
+      <c r="I54" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J54" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" t="s">
+        <v>117</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
+        <v>149</v>
+      </c>
+      <c r="I55" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J55" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>150</v>
+      </c>
+      <c r="B56" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" t="s">
+        <v>152</v>
+      </c>
+      <c r="E56" t="s">
+        <v>117</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>118</v>
+      </c>
+      <c r="H56" t="s">
+        <v>153</v>
+      </c>
+      <c r="I56" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J56" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" t="s">
+        <v>151</v>
+      </c>
+      <c r="D57" t="s">
+        <v>152</v>
+      </c>
+      <c r="E57" t="s">
+        <v>117</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>154</v>
+      </c>
+      <c r="I57" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J57" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" t="s">
+        <v>157</v>
+      </c>
+      <c r="E58" t="s">
+        <v>117</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>118</v>
+      </c>
+      <c r="H58" t="s">
+        <v>158</v>
+      </c>
+      <c r="I58" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J58" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" t="s">
+        <v>156</v>
+      </c>
+      <c r="D59" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s">
+        <v>159</v>
+      </c>
+      <c r="I59" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J59" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>160</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>161</v>
+      </c>
+      <c r="D60" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" t="s">
+        <v>117</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>118</v>
+      </c>
+      <c r="H60" t="s">
+        <v>163</v>
+      </c>
+      <c r="I60" s="3">
+        <v>45717</v>
+      </c>
+      <c r="J60" s="3">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" t="s">
+        <v>161</v>
+      </c>
+      <c r="D61" t="s">
+        <v>162</v>
+      </c>
+      <c r="E61" t="s">
+        <v>117</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" t="s">
+        <v>164</v>
+      </c>
+      <c r="I61" s="3">
+        <v>45870</v>
+      </c>
+      <c r="J61" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="H64" s="2"/>
     </row>
     <row r="65" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H65" s="6"/>
+      <c r="H65" s="2"/>
     </row>
     <row r="66" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H66" s="6"/>
+      <c r="H66" s="2"/>
     </row>
     <row r="67" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H67" s="6"/>
+      <c r="H67" s="2"/>
     </row>
     <row r="68" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H68" s="6"/>
+      <c r="H68" s="2"/>
     </row>
     <row r="69" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H69" s="6"/>
+      <c r="H69" s="2"/>
     </row>
     <row r="70" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H70" s="6"/>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H71" s="6"/>
+      <c r="H71" s="2"/>
     </row>
     <row r="72" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H72" s="6"/>
+      <c r="H72" s="2"/>
     </row>
     <row r="73" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H73" s="6"/>
+      <c r="H73" s="2"/>
     </row>
     <row r="74" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H74" s="6"/>
+      <c r="H74" s="2"/>
     </row>
     <row r="75" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H75" s="6"/>
+      <c r="H75" s="2"/>
     </row>
     <row r="76" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H76" s="6"/>
+      <c r="H76" s="2"/>
     </row>
     <row r="77" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H77" s="6"/>
+      <c r="H77" s="2"/>
     </row>
     <row r="78" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H78" s="6"/>
+      <c r="H78" s="2"/>
     </row>
     <row r="79" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H79" s="6"/>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H80" s="6"/>
+      <c r="H80" s="2"/>
     </row>
     <row r="81" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H81" s="6"/>
+      <c r="H81" s="2"/>
     </row>
     <row r="82" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H82" s="6"/>
+      <c r="H82" s="2"/>
     </row>
     <row r="83" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H83" s="6"/>
+      <c r="H83" s="2"/>
     </row>
     <row r="84" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H84" s="6"/>
+      <c r="H84" s="2"/>
     </row>
     <row r="85" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H85" s="6"/>
+      <c r="H85" s="2"/>
     </row>
     <row r="86" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H86" s="6"/>
+      <c r="H86" s="2"/>
     </row>
     <row r="87" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H87" s="6"/>
+      <c r="H87" s="2"/>
     </row>
     <row r="88" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H88" s="6"/>
+      <c r="H88" s="2"/>
     </row>
     <row r="89" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H89" s="6"/>
+      <c r="H89" s="2"/>
     </row>
     <row r="90" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H90" s="6"/>
+      <c r="H90" s="2"/>
     </row>
     <row r="91" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H91" s="6"/>
+      <c r="H91" s="2"/>
     </row>
     <row r="92" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H92" s="6"/>
+      <c r="H92" s="2"/>
     </row>
     <row r="93" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H93" s="6"/>
+      <c r="H93" s="2"/>
     </row>
     <row r="94" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H94" s="6"/>
+      <c r="H94" s="2"/>
     </row>
     <row r="95" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H95" s="6"/>
+      <c r="H95" s="2"/>
     </row>
     <row r="96" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H96" s="6"/>
+      <c r="H96" s="2"/>
     </row>
     <row r="97" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H97" s="6"/>
+      <c r="H97" s="2"/>
     </row>
     <row r="98" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H98" s="6"/>
+      <c r="H98" s="2"/>
     </row>
     <row r="99" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H99" s="6"/>
+      <c r="H99" s="2"/>
     </row>
     <row r="100" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H100" s="6"/>
+      <c r="H100" s="2"/>
     </row>
     <row r="101" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H101" s="6"/>
+      <c r="H101" s="2"/>
     </row>
     <row r="102" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H102" s="6"/>
+      <c r="H102" s="2"/>
     </row>
     <row r="103" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H103" s="6"/>
+      <c r="H103" s="2"/>
     </row>
     <row r="104" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H104" s="6"/>
+      <c r="H104" s="2"/>
     </row>
     <row r="105" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H105" s="6"/>
+      <c r="H105" s="2"/>
     </row>
     <row r="106" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H106" s="6"/>
+      <c r="H106" s="2"/>
     </row>
     <row r="107" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H107" s="6"/>
+      <c r="H107" s="2"/>
     </row>
     <row r="108" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H108" s="6"/>
+      <c r="H108" s="2"/>
     </row>
     <row r="109" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H109" s="6"/>
+      <c r="H109" s="2"/>
     </row>
     <row r="110" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H110" s="6"/>
+      <c r="H110" s="2"/>
     </row>
     <row r="111" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H111" s="6"/>
+      <c r="H111" s="2"/>
     </row>
     <row r="112" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H112" s="6"/>
+      <c r="H112" s="2"/>
     </row>
     <row r="113" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H113" s="6"/>
+      <c r="H113" s="2"/>
     </row>
     <row r="114" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H114" s="6"/>
+      <c r="H114" s="2"/>
     </row>
     <row r="115" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H115" s="6"/>
+      <c r="H115" s="2"/>
     </row>
     <row r="116" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H116" s="6"/>
+      <c r="H116" s="2"/>
     </row>
     <row r="117" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H117" s="6"/>
+      <c r="H117" s="2"/>
     </row>
     <row r="118" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H118" s="6"/>
+      <c r="H118" s="2"/>
     </row>
     <row r="119" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H119" s="6"/>
+      <c r="H119" s="2"/>
     </row>
     <row r="120" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H120" s="6"/>
+      <c r="H120" s="2"/>
     </row>
     <row r="121" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H121" s="6"/>
+      <c r="H121" s="2"/>
     </row>
     <row r="122" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H122" s="6"/>
+      <c r="H122" s="2"/>
     </row>
     <row r="123" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H123" s="6"/>
+      <c r="H123" s="2"/>
     </row>
     <row r="124" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H124" s="6"/>
+      <c r="H124" s="2"/>
     </row>
     <row r="125" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H125" s="6"/>
+      <c r="H125" s="2"/>
     </row>
     <row r="126" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H126" s="6"/>
+      <c r="H126" s="2"/>
     </row>
     <row r="127" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H127" s="6"/>
+      <c r="H127" s="2"/>
     </row>
     <row r="128" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H128" s="6"/>
+      <c r="H128" s="2"/>
     </row>
     <row r="129" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H129" s="6"/>
+      <c r="H129" s="2"/>
     </row>
     <row r="130" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H130" s="6"/>
+      <c r="H130" s="2"/>
     </row>
     <row r="131" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H131" s="6"/>
+      <c r="H131" s="2"/>
     </row>
     <row r="132" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H132" s="6"/>
+      <c r="H132" s="2"/>
     </row>
     <row r="133" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H133" s="6"/>
+      <c r="H133" s="2"/>
     </row>
     <row r="134" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H134" s="6"/>
+      <c r="H134" s="2"/>
     </row>
     <row r="135" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H135" s="6"/>
+      <c r="H135" s="2"/>
     </row>
     <row r="136" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H136" s="6"/>
+      <c r="H136" s="2"/>
     </row>
     <row r="137" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H137" s="6"/>
+      <c r="H137" s="2"/>
     </row>
     <row r="138" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H138" s="6"/>
+      <c r="H138" s="2"/>
     </row>
     <row r="139" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H139" s="6"/>
+      <c r="H139" s="2"/>
     </row>
     <row r="140" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H140" s="6"/>
+      <c r="H140" s="2"/>
     </row>
     <row r="141" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H141" s="6"/>
+      <c r="H141" s="2"/>
     </row>
     <row r="142" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H142" s="6"/>
+      <c r="H142" s="2"/>
     </row>
     <row r="143" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H143" s="6"/>
+      <c r="H143" s="2"/>
     </row>
     <row r="144" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H144" s="6"/>
+      <c r="H144" s="2"/>
     </row>
     <row r="145" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H145" s="6"/>
+      <c r="H145" s="2"/>
     </row>
     <row r="146" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H146" s="6"/>
+      <c r="H146" s="2"/>
     </row>
     <row r="147" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H147" s="6"/>
+      <c r="H147" s="2"/>
     </row>
     <row r="148" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H148" s="6"/>
+      <c r="H148" s="2"/>
     </row>
     <row r="149" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H149" s="6"/>
+      <c r="H149" s="2"/>
     </row>
     <row r="150" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H150" s="6"/>
+      <c r="H150" s="2"/>
     </row>
     <row r="151" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H151" s="6"/>
+      <c r="H151" s="2"/>
     </row>
     <row r="152" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H152" s="6"/>
+      <c r="H152" s="2"/>
     </row>
     <row r="153" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H153" s="6"/>
+      <c r="H153" s="2"/>
     </row>
     <row r="154" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H154" s="6"/>
+      <c r="H154" s="2"/>
     </row>
     <row r="155" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H155" s="6"/>
+      <c r="H155" s="2"/>
     </row>
     <row r="156" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H156" s="6"/>
+      <c r="H156" s="2"/>
     </row>
     <row r="157" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H157" s="6"/>
+      <c r="H157" s="2"/>
     </row>
     <row r="158" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H158" s="6"/>
+      <c r="H158" s="2"/>
     </row>
     <row r="159" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H159" s="6"/>
+      <c r="H159" s="2"/>
     </row>
     <row r="160" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H160" s="6"/>
+      <c r="H160" s="2"/>
     </row>
     <row r="161" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H161" s="6"/>
+      <c r="H161" s="2"/>
     </row>
     <row r="162" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H162" s="6"/>
+      <c r="H162" s="2"/>
     </row>
     <row r="163" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H163" s="6"/>
+      <c r="H163" s="2"/>
     </row>
     <row r="164" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H164" s="6"/>
+      <c r="H164" s="2"/>
     </row>
     <row r="165" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H165" s="6"/>
+      <c r="H165" s="2"/>
     </row>
     <row r="166" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H166" s="6"/>
+      <c r="H166" s="2"/>
     </row>
     <row r="167" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H167" s="6"/>
+      <c r="H167" s="2"/>
     </row>
     <row r="168" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H168" s="6"/>
+      <c r="H168" s="2"/>
     </row>
     <row r="169" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H169" s="6"/>
+      <c r="H169" s="2"/>
     </row>
     <row r="170" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H170" s="6"/>
+      <c r="H170" s="2"/>
     </row>
     <row r="171" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H171" s="6"/>
+      <c r="H171" s="2"/>
     </row>
     <row r="172" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H172" s="6"/>
+      <c r="H172" s="2"/>
     </row>
     <row r="173" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H173" s="6"/>
+      <c r="H173" s="2"/>
     </row>
     <row r="174" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H174" s="6"/>
+      <c r="H174" s="2"/>
     </row>
     <row r="175" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H175" s="6"/>
+      <c r="H175" s="2"/>
     </row>
     <row r="176" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H176" s="6"/>
+      <c r="H176" s="2"/>
     </row>
     <row r="177" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H177" s="6"/>
+      <c r="H177" s="2"/>
     </row>
     <row r="178" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H178" s="6"/>
+      <c r="H178" s="2"/>
     </row>
     <row r="179" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H179" s="6"/>
+      <c r="H179" s="2"/>
     </row>
     <row r="180" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H180" s="6"/>
+      <c r="H180" s="2"/>
     </row>
     <row r="181" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H181" s="6"/>
+      <c r="H181" s="2"/>
     </row>
     <row r="182" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H182" s="6"/>
+      <c r="H182" s="2"/>
     </row>
     <row r="183" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H183" s="6"/>
+      <c r="H183" s="2"/>
     </row>
     <row r="184" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H184" s="6"/>
+      <c r="H184" s="2"/>
     </row>
     <row r="185" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H185" s="6"/>
+      <c r="H185" s="2"/>
     </row>
     <row r="186" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H186" s="6"/>
+      <c r="H186" s="2"/>
     </row>
     <row r="187" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H187" s="6"/>
+      <c r="H187" s="2"/>
     </row>
     <row r="188" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H188" s="6"/>
+      <c r="H188" s="2"/>
     </row>
     <row r="189" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H189" s="6"/>
+      <c r="H189" s="2"/>
     </row>
     <row r="190" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H190" s="6"/>
+      <c r="H190" s="2"/>
     </row>
     <row r="191" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H191" s="6"/>
+      <c r="H191" s="2"/>
     </row>
     <row r="192" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H192" s="6"/>
+      <c r="H192" s="2"/>
     </row>
     <row r="193" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H193" s="6"/>
+      <c r="H193" s="2"/>
     </row>
     <row r="194" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H194" s="6"/>
+      <c r="H194" s="2"/>
     </row>
     <row r="195" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H195" s="6"/>
+      <c r="H195" s="2"/>
     </row>
     <row r="196" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H196" s="6"/>
+      <c r="H196" s="2"/>
     </row>
     <row r="197" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H197" s="6"/>
+      <c r="H197" s="2"/>
     </row>
     <row r="198" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H198" s="6"/>
+      <c r="H198" s="2"/>
     </row>
     <row r="199" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H199" s="6"/>
+      <c r="H199" s="2"/>
     </row>
     <row r="200" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H200" s="6"/>
+      <c r="H200" s="2"/>
     </row>
     <row r="201" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H201" s="6"/>
+      <c r="H201" s="2"/>
     </row>
     <row r="202" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H202" s="6"/>
+      <c r="H202" s="2"/>
     </row>
     <row r="203" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H203" s="6"/>
+      <c r="H203" s="2"/>
     </row>
     <row r="204" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H204" s="6"/>
+      <c r="H204" s="2"/>
     </row>
     <row r="205" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H205" s="6"/>
+      <c r="H205" s="2"/>
     </row>
     <row r="206" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H206" s="6"/>
+      <c r="H206" s="2"/>
     </row>
     <row r="207" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H207" s="6"/>
+      <c r="H207" s="2"/>
     </row>
     <row r="208" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H208" s="6"/>
+      <c r="H208" s="2"/>
     </row>
     <row r="209" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H209" s="6"/>
+      <c r="H209" s="2"/>
     </row>
     <row r="210" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H210" s="6"/>
+      <c r="H210" s="2"/>
     </row>
     <row r="211" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H211" s="6"/>
+      <c r="H211" s="2"/>
     </row>
     <row r="212" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H212" s="6"/>
+      <c r="H212" s="2"/>
     </row>
     <row r="213" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H213" s="6"/>
+      <c r="H213" s="2"/>
     </row>
     <row r="214" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H214" s="6"/>
+      <c r="H214" s="2"/>
     </row>
     <row r="215" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H215" s="6"/>
+      <c r="H215" s="2"/>
     </row>
     <row r="216" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H216" s="6"/>
+      <c r="H216" s="2"/>
     </row>
     <row r="217" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H217" s="6"/>
+      <c r="H217" s="2"/>
     </row>
     <row r="218" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H218" s="6"/>
+      <c r="H218" s="2"/>
     </row>
     <row r="219" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H219" s="6"/>
+      <c r="H219" s="2"/>
     </row>
     <row r="220" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H220" s="6"/>
+      <c r="H220" s="2"/>
     </row>
     <row r="221" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H221" s="6"/>
+      <c r="H221" s="2"/>
     </row>
     <row r="222" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H222" s="6"/>
+      <c r="H222" s="2"/>
     </row>
     <row r="223" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H223" s="6"/>
+      <c r="H223" s="2"/>
     </row>
     <row r="224" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H224" s="6"/>
+      <c r="H224" s="2"/>
     </row>
     <row r="225" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H225" s="6"/>
+      <c r="H225" s="2"/>
     </row>
     <row r="226" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H226" s="6"/>
+      <c r="H226" s="2"/>
     </row>
     <row r="227" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H227" s="6"/>
+      <c r="H227" s="2"/>
     </row>
     <row r="228" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H228" s="6"/>
+      <c r="H228" s="2"/>
     </row>
     <row r="229" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H229" s="6"/>
+      <c r="H229" s="2"/>
     </row>
     <row r="230" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H230" s="6"/>
+      <c r="H230" s="2"/>
     </row>
     <row r="231" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H231" s="6"/>
+      <c r="H231" s="2"/>
     </row>
     <row r="232" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H232" s="6"/>
+      <c r="H232" s="2"/>
     </row>
     <row r="233" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H233" s="6"/>
+      <c r="H233" s="2"/>
     </row>
     <row r="234" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H234" s="6"/>
+      <c r="H234" s="2"/>
     </row>
     <row r="235" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H235" s="6"/>
+      <c r="H235" s="2"/>
     </row>
     <row r="236" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H236" s="6"/>
+      <c r="H236" s="2"/>
     </row>
     <row r="237" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H237" s="6"/>
+      <c r="H237" s="2"/>
     </row>
     <row r="238" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H238" s="6"/>
+      <c r="H238" s="2"/>
     </row>
     <row r="239" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H239" s="6"/>
+      <c r="H239" s="2"/>
     </row>
     <row r="240" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H240" s="6"/>
+      <c r="H240" s="2"/>
     </row>
     <row r="241" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H241" s="6"/>
+      <c r="H241" s="2"/>
     </row>
     <row r="242" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H242" s="6"/>
+      <c r="H242" s="2"/>
     </row>
     <row r="243" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H243" s="6"/>
+      <c r="H243" s="2"/>
     </row>
     <row r="244" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H244" s="6"/>
+      <c r="H244" s="2"/>
     </row>
     <row r="245" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H245" s="6"/>
+      <c r="H245" s="2"/>
     </row>
     <row r="246" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H246" s="6"/>
+      <c r="H246" s="2"/>
     </row>
     <row r="247" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H247" s="6"/>
+      <c r="H247" s="2"/>
     </row>
     <row r="248" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H248" s="6"/>
+      <c r="H248" s="2"/>
     </row>
     <row r="249" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H249" s="6"/>
+      <c r="H249" s="2"/>
     </row>
     <row r="250" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H250" s="6"/>
+      <c r="H250" s="2"/>
     </row>
     <row r="251" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H251" s="6"/>
+      <c r="H251" s="2"/>
     </row>
     <row r="252" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H252" s="6"/>
+      <c r="H252" s="2"/>
     </row>
     <row r="253" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H253" s="6"/>
+      <c r="H253" s="2"/>
     </row>
     <row r="254" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H254" s="6"/>
+      <c r="H254" s="2"/>
     </row>
     <row r="255" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H255" s="6"/>
+      <c r="H255" s="2"/>
     </row>
     <row r="256" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H256" s="6"/>
+      <c r="H256" s="2"/>
     </row>
     <row r="257" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H257" s="6"/>
+      <c r="H257" s="2"/>
     </row>
     <row r="258" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H258" s="6"/>
+      <c r="H258" s="2"/>
     </row>
     <row r="259" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H259" s="6"/>
+      <c r="H259" s="2"/>
     </row>
     <row r="260" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H260" s="6"/>
+      <c r="H260" s="2"/>
     </row>
     <row r="261" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H261" s="6"/>
+      <c r="H261" s="2"/>
     </row>
     <row r="262" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H262" s="6"/>
+      <c r="H262" s="2"/>
     </row>
     <row r="263" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H263" s="6"/>
+      <c r="H263" s="2"/>
     </row>
     <row r="264" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H264" s="6"/>
+      <c r="H264" s="2"/>
     </row>
     <row r="265" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H265" s="6"/>
+      <c r="H265" s="2"/>
     </row>
     <row r="266" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H266" s="6"/>
+      <c r="H266" s="2"/>
     </row>
     <row r="267" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H267" s="6"/>
+      <c r="H267" s="2"/>
     </row>
     <row r="268" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H268" s="6"/>
+      <c r="H268" s="2"/>
     </row>
     <row r="269" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H269" s="6"/>
+      <c r="H269" s="2"/>
     </row>
     <row r="270" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H270" s="6"/>
+      <c r="H270" s="2"/>
     </row>
     <row r="271" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H271" s="6"/>
+      <c r="H271" s="2"/>
     </row>
     <row r="272" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H272" s="6"/>
+      <c r="H272" s="2"/>
     </row>
     <row r="273" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H273" s="6"/>
+      <c r="H273" s="2"/>
     </row>
     <row r="274" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H274" s="6"/>
+      <c r="H274" s="2"/>
     </row>
     <row r="275" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H275" s="6"/>
+      <c r="H275" s="2"/>
     </row>
     <row r="276" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H276" s="6"/>
+      <c r="H276" s="2"/>
     </row>
     <row r="277" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H277" s="6"/>
+      <c r="H277" s="2"/>
     </row>
     <row r="278" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H278" s="6"/>
+      <c r="H278" s="2"/>
     </row>
     <row r="279" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H279" s="6"/>
+      <c r="H279" s="2"/>
     </row>
     <row r="280" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H280" s="6"/>
+      <c r="H280" s="2"/>
     </row>
     <row r="281" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H281" s="6"/>
+      <c r="H281" s="2"/>
     </row>
     <row r="282" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H282" s="6"/>
+      <c r="H282" s="2"/>
     </row>
     <row r="283" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H283" s="6"/>
+      <c r="H283" s="2"/>
     </row>
     <row r="284" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H284" s="6"/>
+      <c r="H284" s="2"/>
     </row>
     <row r="285" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H285" s="6"/>
+      <c r="H285" s="2"/>
     </row>
     <row r="286" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H286" s="6"/>
+      <c r="H286" s="2"/>
     </row>
     <row r="287" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H287" s="6"/>
+      <c r="H287" s="2"/>
     </row>
     <row r="288" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H288" s="6"/>
+      <c r="H288" s="2"/>
     </row>
     <row r="289" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H289" s="6"/>
+      <c r="H289" s="2"/>
     </row>
     <row r="290" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H290" s="6"/>
+      <c r="H290" s="2"/>
     </row>
     <row r="291" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H291" s="6"/>
+      <c r="H291" s="2"/>
     </row>
     <row r="292" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H292" s="6"/>
+      <c r="H292" s="2"/>
     </row>
     <row r="293" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H293" s="6"/>
+      <c r="H293" s="2"/>
     </row>
     <row r="294" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H294" s="6"/>
+      <c r="H294" s="2"/>
     </row>
     <row r="295" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H295" s="6"/>
+      <c r="H295" s="2"/>
     </row>
     <row r="296" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H296" s="6"/>
+      <c r="H296" s="2"/>
     </row>
     <row r="297" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H297" s="6"/>
+      <c r="H297" s="2"/>
     </row>
     <row r="298" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H298" s="6"/>
+      <c r="H298" s="2"/>
     </row>
     <row r="299" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H299" s="6"/>
+      <c r="H299" s="2"/>
     </row>
     <row r="300" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H300" s="6"/>
+      <c r="H300" s="2"/>
     </row>
     <row r="301" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H301" s="6"/>
+      <c r="H301" s="2"/>
     </row>
     <row r="302" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H302" s="6"/>
+      <c r="H302" s="2"/>
     </row>
     <row r="303" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H303" s="6"/>
+      <c r="H303" s="2"/>
     </row>
     <row r="304" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H304" s="6"/>
+      <c r="H304" s="2"/>
     </row>
     <row r="305" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H305" s="6"/>
+      <c r="H305" s="2"/>
     </row>
     <row r="306" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H306" s="6"/>
+      <c r="H306" s="2"/>
     </row>
     <row r="307" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H307" s="6"/>
+      <c r="H307" s="2"/>
     </row>
     <row r="308" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H308" s="6"/>
+      <c r="H308" s="2"/>
     </row>
     <row r="309" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H309" s="6"/>
+      <c r="H309" s="2"/>
     </row>
     <row r="310" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H310" s="6"/>
+      <c r="H310" s="2"/>
     </row>
     <row r="311" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H311" s="6"/>
+      <c r="H311" s="2"/>
     </row>
     <row r="312" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H312" s="6"/>
+      <c r="H312" s="2"/>
     </row>
     <row r="313" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H313" s="6"/>
+      <c r="H313" s="2"/>
     </row>
     <row r="314" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H314" s="6"/>
+      <c r="H314" s="2"/>
     </row>
     <row r="315" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H315" s="6"/>
+      <c r="H315" s="2"/>
     </row>
     <row r="316" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H316" s="6"/>
+      <c r="H316" s="2"/>
     </row>
     <row r="317" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H317" s="6"/>
+      <c r="H317" s="2"/>
     </row>
     <row r="318" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H318" s="6"/>
+      <c r="H318" s="2"/>
     </row>
     <row r="319" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H319" s="6"/>
+      <c r="H319" s="2"/>
     </row>
     <row r="320" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H320" s="6"/>
+      <c r="H320" s="2"/>
     </row>
     <row r="321" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H321" s="6"/>
+      <c r="H321" s="2"/>
     </row>
     <row r="322" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H322" s="6"/>
+      <c r="H322" s="2"/>
     </row>
     <row r="323" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H323" s="6"/>
+      <c r="H323" s="2"/>
     </row>
     <row r="324" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H324" s="6"/>
+      <c r="H324" s="2"/>
     </row>
     <row r="325" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H325" s="6"/>
+      <c r="H325" s="2"/>
     </row>
     <row r="326" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H326" s="6"/>
+      <c r="H326" s="2"/>
     </row>
     <row r="327" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H327" s="6"/>
+      <c r="H327" s="2"/>
     </row>
     <row r="328" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H328" s="6"/>
+      <c r="H328" s="2"/>
     </row>
     <row r="329" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H329" s="6"/>
+      <c r="H329" s="2"/>
     </row>
     <row r="330" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H330" s="6"/>
+      <c r="H330" s="2"/>
     </row>
     <row r="331" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H331" s="6"/>
+      <c r="H331" s="2"/>
     </row>
     <row r="332" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H332" s="6"/>
+      <c r="H332" s="2"/>
     </row>
     <row r="333" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H333" s="6"/>
+      <c r="H333" s="2"/>
     </row>
     <row r="334" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H334" s="6"/>
+      <c r="H334" s="2"/>
     </row>
     <row r="335" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H335" s="6"/>
+      <c r="H335" s="2"/>
     </row>
     <row r="336" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H336" s="6"/>
+      <c r="H336" s="2"/>
     </row>
     <row r="337" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H337" s="6"/>
+      <c r="H337" s="2"/>
     </row>
     <row r="338" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H338" s="6"/>
+      <c r="H338" s="2"/>
     </row>
     <row r="339" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H339" s="6"/>
+      <c r="H339" s="2"/>
     </row>
     <row r="340" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H340" s="6"/>
+      <c r="H340" s="2"/>
     </row>
     <row r="341" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H341" s="6"/>
+      <c r="H341" s="2"/>
     </row>
     <row r="342" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H342" s="6"/>
+      <c r="H342" s="2"/>
     </row>
     <row r="343" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H343" s="6"/>
+      <c r="H343" s="2"/>
     </row>
     <row r="344" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H344" s="6"/>
+      <c r="H344" s="2"/>
     </row>
     <row r="345" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H345" s="6"/>
+      <c r="H345" s="2"/>
     </row>
     <row r="346" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H346" s="6"/>
+      <c r="H346" s="2"/>
     </row>
     <row r="347" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H347" s="6"/>
+      <c r="H347" s="2"/>
     </row>
     <row r="348" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H348" s="6"/>
+      <c r="H348" s="2"/>
     </row>
     <row r="349" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H349" s="6"/>
+      <c r="H349" s="2"/>
     </row>
     <row r="350" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H350" s="6"/>
+      <c r="H350" s="2"/>
     </row>
     <row r="351" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H351" s="6"/>
+      <c r="H351" s="2"/>
     </row>
     <row r="352" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H352" s="6"/>
+      <c r="H352" s="2"/>
     </row>
     <row r="353" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H353" s="6"/>
+      <c r="H353" s="2"/>
     </row>
     <row r="354" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H354" s="6"/>
+      <c r="H354" s="2"/>
     </row>
     <row r="355" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H355" s="6"/>
+      <c r="H355" s="2"/>
     </row>
     <row r="356" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H356" s="6"/>
+      <c r="H356" s="2"/>
     </row>
     <row r="357" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H357" s="6"/>
+      <c r="H357" s="2"/>
     </row>
     <row r="358" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H358" s="6"/>
+      <c r="H358" s="2"/>
     </row>
     <row r="359" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H359" s="6"/>
+      <c r="H359" s="2"/>
     </row>
     <row r="360" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H360" s="6"/>
+      <c r="H360" s="2"/>
     </row>
     <row r="361" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H361" s="6"/>
+      <c r="H361" s="2"/>
     </row>
     <row r="362" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H362" s="6"/>
+      <c r="H362" s="2"/>
     </row>
     <row r="363" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H363" s="6"/>
+      <c r="H363" s="2"/>
     </row>
     <row r="364" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H364" s="6"/>
+      <c r="H364" s="2"/>
     </row>
     <row r="365" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H365" s="6"/>
+      <c r="H365" s="2"/>
     </row>
     <row r="366" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H366" s="6"/>
+      <c r="H366" s="2"/>
     </row>
     <row r="367" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H367" s="6"/>
+      <c r="H367" s="2"/>
     </row>
     <row r="368" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H368" s="6"/>
+      <c r="H368" s="2"/>
     </row>
     <row r="369" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H369" s="6"/>
+      <c r="H369" s="2"/>
     </row>
     <row r="370" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H370" s="6"/>
+      <c r="H370" s="2"/>
     </row>
     <row r="371" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H371" s="6"/>
+      <c r="H371" s="2"/>
     </row>
     <row r="372" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H372" s="6"/>
+      <c r="H372" s="2"/>
     </row>
     <row r="373" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H373" s="6"/>
+      <c r="H373" s="2"/>
     </row>
     <row r="374" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H374" s="6"/>
+      <c r="H374" s="2"/>
     </row>
     <row r="375" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H375" s="6"/>
+      <c r="H375" s="2"/>
     </row>
     <row r="376" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H376" s="6"/>
+      <c r="H376" s="2"/>
     </row>
     <row r="377" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H377" s="6"/>
+      <c r="H377" s="2"/>
     </row>
     <row r="378" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H378" s="6"/>
+      <c r="H378" s="2"/>
     </row>
     <row r="379" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H379" s="6"/>
+      <c r="H379" s="2"/>
     </row>
     <row r="380" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H380" s="6"/>
+      <c r="H380" s="2"/>
     </row>
     <row r="381" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H381" s="6"/>
+      <c r="H381" s="2"/>
     </row>
     <row r="382" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H382" s="6"/>
+      <c r="H382" s="2"/>
     </row>
     <row r="383" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H383" s="6"/>
+      <c r="H383" s="2"/>
     </row>
     <row r="384" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H384" s="6"/>
+      <c r="H384" s="2"/>
     </row>
     <row r="385" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H385" s="6"/>
+      <c r="H385" s="2"/>
     </row>
     <row r="386" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H386" s="6"/>
+      <c r="H386" s="2"/>
     </row>
     <row r="387" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H387" s="6"/>
+      <c r="H387" s="2"/>
     </row>
     <row r="388" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H388" s="6"/>
+      <c r="H388" s="2"/>
     </row>
     <row r="389" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H389" s="6"/>
+      <c r="H389" s="2"/>
     </row>
     <row r="390" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H390" s="6"/>
+      <c r="H390" s="2"/>
     </row>
     <row r="391" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H391" s="6"/>
+      <c r="H391" s="2"/>
     </row>
     <row r="392" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H392" s="6"/>
+      <c r="H392" s="2"/>
     </row>
     <row r="393" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H393" s="6"/>
+      <c r="H393" s="2"/>
     </row>
     <row r="394" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H394" s="6"/>
+      <c r="H394" s="2"/>
     </row>
     <row r="395" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H395" s="6"/>
+      <c r="H395" s="2"/>
     </row>
     <row r="396" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H396" s="6"/>
+      <c r="H396" s="2"/>
     </row>
     <row r="397" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H397" s="6"/>
+      <c r="H397" s="2"/>
     </row>
     <row r="398" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H398" s="6"/>
+      <c r="H398" s="2"/>
     </row>
     <row r="399" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H399" s="6"/>
+      <c r="H399" s="2"/>
     </row>
     <row r="400" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H400" s="6"/>
+      <c r="H400" s="2"/>
     </row>
     <row r="401" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H401" s="6"/>
+      <c r="H401" s="2"/>
     </row>
     <row r="402" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H402" s="6"/>
+      <c r="H402" s="2"/>
     </row>
     <row r="403" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H403" s="6"/>
+      <c r="H403" s="2"/>
     </row>
     <row r="404" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H404" s="6"/>
+      <c r="H404" s="2"/>
     </row>
     <row r="405" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H405" s="6"/>
+      <c r="H405" s="2"/>
     </row>
     <row r="406" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H406" s="6"/>
+      <c r="H406" s="2"/>
     </row>
     <row r="407" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H407" s="6"/>
+      <c r="H407" s="2"/>
     </row>
     <row r="408" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H408" s="6"/>
+      <c r="H408" s="2"/>
     </row>
     <row r="409" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H409" s="6"/>
+      <c r="H409" s="2"/>
     </row>
     <row r="410" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H410" s="6"/>
+      <c r="H410" s="2"/>
     </row>
     <row r="411" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H411" s="6"/>
+      <c r="H411" s="2"/>
     </row>
     <row r="412" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H412" s="6"/>
+      <c r="H412" s="2"/>
     </row>
     <row r="413" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H413" s="6"/>
+      <c r="H413" s="2"/>
     </row>
     <row r="414" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H414" s="6"/>
+      <c r="H414" s="2"/>
     </row>
     <row r="415" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H415" s="6"/>
+      <c r="H415" s="2"/>
     </row>
     <row r="416" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H416" s="6"/>
+      <c r="H416" s="2"/>
     </row>
     <row r="417" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H417" s="6"/>
+      <c r="H417" s="2"/>
     </row>
     <row r="418" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H418" s="6"/>
+      <c r="H418" s="2"/>
     </row>
     <row r="419" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H419" s="6"/>
+      <c r="H419" s="2"/>
     </row>
     <row r="420" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H420" s="6"/>
+      <c r="H420" s="2"/>
     </row>
     <row r="421" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H421" s="6"/>
+      <c r="H421" s="2"/>
     </row>
     <row r="422" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H422" s="6"/>
+      <c r="H422" s="2"/>
     </row>
     <row r="423" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H423" s="6"/>
+      <c r="H423" s="2"/>
     </row>
     <row r="424" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H424" s="6"/>
+      <c r="H424" s="2"/>
     </row>
     <row r="425" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H425" s="6"/>
+      <c r="H425" s="2"/>
     </row>
     <row r="426" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H426" s="6"/>
+      <c r="H426" s="2"/>
     </row>
     <row r="427" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H427" s="6"/>
+      <c r="H427" s="2"/>
     </row>
     <row r="428" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H428" s="6"/>
+      <c r="H428" s="2"/>
     </row>
     <row r="429" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H429" s="6"/>
+      <c r="H429" s="2"/>
     </row>
     <row r="430" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H430" s="6"/>
+      <c r="H430" s="2"/>
     </row>
     <row r="431" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H431" s="6"/>
+      <c r="H431" s="2"/>
     </row>
     <row r="432" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H432" s="6"/>
+      <c r="H432" s="2"/>
     </row>
     <row r="433" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H433" s="6"/>
+      <c r="H433" s="2"/>
     </row>
     <row r="434" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H434" s="6"/>
+      <c r="H434" s="2"/>
     </row>
     <row r="435" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H435" s="6"/>
+      <c r="H435" s="2"/>
     </row>
     <row r="436" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H436" s="6"/>
+      <c r="H436" s="2"/>
     </row>
     <row r="437" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H437" s="6"/>
+      <c r="H437" s="2"/>
     </row>
     <row r="438" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H438" s="6"/>
+      <c r="H438" s="2"/>
     </row>
     <row r="439" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H439" s="6"/>
+      <c r="H439" s="2"/>
     </row>
     <row r="440" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H440" s="6"/>
+      <c r="H440" s="2"/>
     </row>
     <row r="441" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H441" s="6"/>
+      <c r="H441" s="2"/>
     </row>
     <row r="442" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H442" s="6"/>
+      <c r="H442" s="2"/>
     </row>
     <row r="443" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H443" s="6"/>
+      <c r="H443" s="2"/>
     </row>
     <row r="444" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H444" s="6"/>
+      <c r="H444" s="2"/>
     </row>
     <row r="445" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H445" s="6"/>
+      <c r="H445" s="2"/>
     </row>
     <row r="446" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H446" s="6"/>
+      <c r="H446" s="2"/>
     </row>
     <row r="447" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H447" s="6"/>
+      <c r="H447" s="2"/>
     </row>
     <row r="448" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H448" s="6"/>
+      <c r="H448" s="2"/>
     </row>
     <row r="449" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H449" s="6"/>
+      <c r="H449" s="2"/>
     </row>
     <row r="450" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H450" s="6"/>
+      <c r="H450" s="2"/>
     </row>
     <row r="451" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H451" s="6"/>
+      <c r="H451" s="2"/>
     </row>
     <row r="452" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H452" s="6"/>
+      <c r="H452" s="2"/>
     </row>
     <row r="453" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H453" s="6"/>
+      <c r="H453" s="2"/>
     </row>
     <row r="454" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H454" s="6"/>
+      <c r="H454" s="2"/>
     </row>
     <row r="455" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H455" s="6"/>
+      <c r="H455" s="2"/>
     </row>
     <row r="456" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H456" s="6"/>
+      <c r="H456" s="2"/>
     </row>
     <row r="457" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H457" s="6"/>
+      <c r="H457" s="2"/>
     </row>
     <row r="458" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H458" s="6"/>
+      <c r="H458" s="2"/>
     </row>
     <row r="459" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H459" s="6"/>
+      <c r="H459" s="2"/>
     </row>
     <row r="460" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H460" s="6"/>
+      <c r="H460" s="2"/>
     </row>
     <row r="461" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H461" s="6"/>
+      <c r="H461" s="2"/>
     </row>
     <row r="462" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H462" s="6"/>
+      <c r="H462" s="2"/>
     </row>
     <row r="463" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H463" s="6"/>
+      <c r="H463" s="2"/>
     </row>
     <row r="464" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H464" s="6"/>
+      <c r="H464" s="2"/>
     </row>
     <row r="465" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H465" s="6"/>
+      <c r="H465" s="2"/>
     </row>
     <row r="466" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H466" s="6"/>
+      <c r="H466" s="2"/>
     </row>
     <row r="467" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H467" s="6"/>
+      <c r="H467" s="2"/>
     </row>
     <row r="468" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H468" s="6"/>
+      <c r="H468" s="2"/>
     </row>
     <row r="469" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H469" s="6"/>
+      <c r="H469" s="2"/>
     </row>
     <row r="470" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H470" s="6"/>
+      <c r="H470" s="2"/>
     </row>
     <row r="471" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H471" s="6"/>
+      <c r="H471" s="2"/>
     </row>
     <row r="472" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H472" s="6"/>
+      <c r="H472" s="2"/>
     </row>
     <row r="473" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H473" s="6"/>
+      <c r="H473" s="2"/>
     </row>
     <row r="474" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H474" s="6"/>
+      <c r="H474" s="2"/>
     </row>
     <row r="475" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H475" s="6"/>
+      <c r="H475" s="2"/>
     </row>
     <row r="476" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H476" s="6"/>
+      <c r="H476" s="2"/>
     </row>
     <row r="477" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H477" s="6"/>
+      <c r="H477" s="2"/>
     </row>
     <row r="478" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H478" s="6"/>
+      <c r="H478" s="2"/>
     </row>
     <row r="479" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H479" s="6"/>
+      <c r="H479" s="2"/>
     </row>
     <row r="480" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H480" s="6"/>
+      <c r="H480" s="2"/>
     </row>
     <row r="481" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H481" s="6"/>
+      <c r="H481" s="2"/>
     </row>
     <row r="482" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H482" s="6"/>
+      <c r="H482" s="2"/>
     </row>
     <row r="483" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H483" s="6"/>
+      <c r="H483" s="2"/>
     </row>
     <row r="484" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H484" s="6"/>
+      <c r="H484" s="2"/>
     </row>
     <row r="485" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H485" s="6"/>
+      <c r="H485" s="2"/>
     </row>
     <row r="486" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H486" s="6"/>
+      <c r="H486" s="2"/>
     </row>
     <row r="487" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H487" s="6"/>
+      <c r="H487" s="2"/>
     </row>
     <row r="488" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H488" s="6"/>
+      <c r="H488" s="2"/>
     </row>
     <row r="489" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H489" s="6"/>
+      <c r="H489" s="2"/>
     </row>
     <row r="490" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H490" s="6"/>
+      <c r="H490" s="2"/>
     </row>
     <row r="491" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H491" s="6"/>
+      <c r="H491" s="2"/>
     </row>
     <row r="492" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H492" s="6"/>
+      <c r="H492" s="2"/>
     </row>
     <row r="493" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H493" s="6"/>
+      <c r="H493" s="2"/>
     </row>
     <row r="494" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H494" s="6"/>
+      <c r="H494" s="2"/>
     </row>
     <row r="495" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H495" s="6"/>
+      <c r="H495" s="2"/>
     </row>
     <row r="496" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H496" s="6"/>
+      <c r="H496" s="2"/>
     </row>
     <row r="497" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H497" s="6"/>
+      <c r="H497" s="2"/>
     </row>
     <row r="498" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H498" s="6"/>
+      <c r="H498" s="2"/>
     </row>
     <row r="499" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H499" s="6"/>
+      <c r="H499" s="2"/>
     </row>
     <row r="500" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H500" s="6"/>
+      <c r="H500" s="2"/>
     </row>
     <row r="501" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H501" s="6"/>
+      <c r="H501" s="2"/>
     </row>
     <row r="502" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H502" s="6"/>
+      <c r="H502" s="2"/>
     </row>
     <row r="503" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H503" s="6"/>
+      <c r="H503" s="2"/>
     </row>
     <row r="504" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H504" s="6"/>
+      <c r="H504" s="2"/>
     </row>
     <row r="505" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H505" s="6"/>
+      <c r="H505" s="2"/>
     </row>
     <row r="506" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H506" s="6"/>
+      <c r="H506" s="2"/>
     </row>
     <row r="507" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H507" s="6"/>
+      <c r="H507" s="2"/>
     </row>
     <row r="508" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H508" s="6"/>
+      <c r="H508" s="2"/>
     </row>
     <row r="509" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H509" s="6"/>
+      <c r="H509" s="2"/>
     </row>
     <row r="510" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H510" s="6"/>
+      <c r="H510" s="2"/>
     </row>
     <row r="511" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H511" s="6"/>
+      <c r="H511" s="2"/>
     </row>
     <row r="512" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H512" s="6"/>
+      <c r="H512" s="2"/>
     </row>
     <row r="513" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H513" s="6"/>
+      <c r="H513" s="2"/>
     </row>
     <row r="514" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H514" s="6"/>
+      <c r="H514" s="2"/>
     </row>
     <row r="515" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H515" s="6"/>
+      <c r="H515" s="2"/>
     </row>
     <row r="516" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H516" s="6"/>
+      <c r="H516" s="2"/>
     </row>
     <row r="517" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H517" s="6"/>
+      <c r="H517" s="2"/>
     </row>
     <row r="518" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H518" s="6"/>
+      <c r="H518" s="2"/>
     </row>
     <row r="519" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H519" s="6"/>
+      <c r="H519" s="2"/>
     </row>
     <row r="520" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H520" s="6"/>
+      <c r="H520" s="2"/>
     </row>
     <row r="521" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H521" s="6"/>
+      <c r="H521" s="2"/>
     </row>
     <row r="522" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H522" s="6"/>
+      <c r="H522" s="2"/>
     </row>
     <row r="523" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H523" s="6"/>
+      <c r="H523" s="2"/>
     </row>
     <row r="524" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H524" s="6"/>
+      <c r="H524" s="2"/>
     </row>
     <row r="525" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H525" s="6"/>
+      <c r="H525" s="2"/>
     </row>
     <row r="526" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H526" s="6"/>
+      <c r="H526" s="2"/>
     </row>
     <row r="527" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H527" s="6"/>
+      <c r="H527" s="2"/>
     </row>
     <row r="528" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H528" s="6"/>
+      <c r="H528" s="2"/>
     </row>
     <row r="529" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H529" s="6"/>
+      <c r="H529" s="2"/>
     </row>
     <row r="530" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H530" s="6"/>
+      <c r="H530" s="2"/>
     </row>
     <row r="531" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H531" s="6"/>
+      <c r="H531" s="2"/>
     </row>
     <row r="532" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H532" s="6"/>
+      <c r="H532" s="2"/>
     </row>
     <row r="533" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H533" s="6"/>
+      <c r="H533" s="2"/>
     </row>
     <row r="534" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H534" s="6"/>
+      <c r="H534" s="2"/>
     </row>
     <row r="535" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H535" s="6"/>
+      <c r="H535" s="2"/>
     </row>
     <row r="536" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H536" s="6"/>
+      <c r="H536" s="2"/>
     </row>
     <row r="537" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H537" s="6"/>
+      <c r="H537" s="2"/>
     </row>
     <row r="538" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H538" s="6"/>
+      <c r="H538" s="2"/>
     </row>
     <row r="539" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H539" s="6"/>
+      <c r="H539" s="2"/>
     </row>
     <row r="540" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H540" s="6"/>
+      <c r="H540" s="2"/>
     </row>
     <row r="541" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H541" s="6"/>
+      <c r="H541" s="2"/>
     </row>
     <row r="542" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H542" s="6"/>
+      <c r="H542" s="2"/>
     </row>
     <row r="543" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H543" s="6"/>
+      <c r="H543" s="2"/>
     </row>
     <row r="544" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H544" s="6"/>
+      <c r="H544" s="2"/>
     </row>
     <row r="545" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H545" s="6"/>
+      <c r="H545" s="2"/>
     </row>
     <row r="546" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H546" s="6"/>
+      <c r="H546" s="2"/>
     </row>
     <row r="547" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H547" s="6"/>
+      <c r="H547" s="2"/>
     </row>
     <row r="548" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H548" s="6"/>
+      <c r="H548" s="2"/>
     </row>
     <row r="549" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H549" s="6"/>
+      <c r="H549" s="2"/>
     </row>
     <row r="550" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H550" s="6"/>
+      <c r="H550" s="2"/>
     </row>
     <row r="551" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H551" s="6"/>
+      <c r="H551" s="2"/>
     </row>
     <row r="552" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H552" s="6"/>
+      <c r="H552" s="2"/>
     </row>
     <row r="553" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H553" s="6"/>
+      <c r="H553" s="2"/>
     </row>
     <row r="554" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H554" s="6"/>
+      <c r="H554" s="2"/>
     </row>
     <row r="555" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H555" s="6"/>
+      <c r="H555" s="2"/>
     </row>
     <row r="556" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H556" s="6"/>
+      <c r="H556" s="2"/>
     </row>
     <row r="557" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H557" s="6"/>
+      <c r="H557" s="2"/>
     </row>
     <row r="558" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H558" s="6"/>
+      <c r="H558" s="2"/>
     </row>
     <row r="559" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H559" s="6"/>
+      <c r="H559" s="2"/>
     </row>
     <row r="560" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H560" s="6"/>
+      <c r="H560" s="2"/>
     </row>
     <row r="561" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H561" s="6"/>
+      <c r="H561" s="2"/>
     </row>
     <row r="562" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H562" s="6"/>
+      <c r="H562" s="2"/>
     </row>
     <row r="563" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H563" s="6"/>
+      <c r="H563" s="2"/>
     </row>
     <row r="564" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H564" s="6"/>
+      <c r="H564" s="2"/>
     </row>
     <row r="565" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H565" s="6"/>
+      <c r="H565" s="2"/>
     </row>
     <row r="566" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H566" s="6"/>
+      <c r="H566" s="2"/>
     </row>
     <row r="567" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H567" s="6"/>
+      <c r="H567" s="2"/>
     </row>
     <row r="568" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H568" s="6"/>
+      <c r="H568" s="2"/>
     </row>
     <row r="569" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H569" s="6"/>
+      <c r="H569" s="2"/>
     </row>
     <row r="570" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H570" s="6"/>
+      <c r="H570" s="2"/>
     </row>
     <row r="571" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H571" s="6"/>
+      <c r="H571" s="2"/>
     </row>
     <row r="572" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H572" s="6"/>
+      <c r="H572" s="2"/>
     </row>
     <row r="573" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H573" s="6"/>
+      <c r="H573" s="2"/>
     </row>
     <row r="574" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H574" s="6"/>
+      <c r="H574" s="2"/>
     </row>
     <row r="575" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H575" s="6"/>
+      <c r="H575" s="2"/>
     </row>
     <row r="576" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H576" s="6"/>
+      <c r="H576" s="2"/>
     </row>
     <row r="577" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H577" s="6"/>
+      <c r="H577" s="2"/>
     </row>
     <row r="578" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H578" s="6"/>
+      <c r="H578" s="2"/>
     </row>
     <row r="579" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H579" s="6"/>
+      <c r="H579" s="2"/>
     </row>
     <row r="580" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H580" s="6"/>
+      <c r="H580" s="2"/>
     </row>
     <row r="581" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H581" s="6"/>
+      <c r="H581" s="2"/>
     </row>
     <row r="582" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H582" s="6"/>
+      <c r="H582" s="2"/>
     </row>
     <row r="583" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H583" s="6"/>
+      <c r="H583" s="2"/>
     </row>
     <row r="584" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H584" s="6"/>
+      <c r="H584" s="2"/>
     </row>
     <row r="585" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H585" s="6"/>
+      <c r="H585" s="2"/>
     </row>
     <row r="586" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H586" s="6"/>
+      <c r="H586" s="2"/>
     </row>
     <row r="587" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H587" s="6"/>
+      <c r="H587" s="2"/>
     </row>
     <row r="588" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H588" s="6"/>
+      <c r="H588" s="2"/>
     </row>
     <row r="589" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H589" s="6"/>
+      <c r="H589" s="2"/>
     </row>
     <row r="590" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H590" s="6"/>
+      <c r="H590" s="2"/>
     </row>
     <row r="591" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H591" s="6"/>
+      <c r="H591" s="2"/>
     </row>
     <row r="592" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H592" s="6"/>
+      <c r="H592" s="2"/>
     </row>
     <row r="593" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H593" s="6"/>
+      <c r="H593" s="2"/>
     </row>
     <row r="594" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H594" s="6"/>
+      <c r="H594" s="2"/>
     </row>
     <row r="595" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H595" s="6"/>
+      <c r="H595" s="2"/>
     </row>
     <row r="596" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H596" s="6"/>
+      <c r="H596" s="2"/>
     </row>
     <row r="597" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H597" s="6"/>
+      <c r="H597" s="2"/>
     </row>
     <row r="598" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H598" s="6"/>
+      <c r="H598" s="2"/>
     </row>
     <row r="599" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H599" s="6"/>
+      <c r="H599" s="2"/>
     </row>
     <row r="600" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H600" s="6"/>
+      <c r="H600" s="2"/>
     </row>
     <row r="601" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H601" s="6"/>
+      <c r="H601" s="2"/>
     </row>
     <row r="602" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H602" s="6"/>
+      <c r="H602" s="2"/>
     </row>
     <row r="603" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H603" s="6"/>
+      <c r="H603" s="2"/>
     </row>
     <row r="604" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H604" s="6"/>
+      <c r="H604" s="2"/>
     </row>
     <row r="605" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H605" s="6"/>
+      <c r="H605" s="2"/>
     </row>
     <row r="606" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H606" s="6"/>
+      <c r="H606" s="2"/>
     </row>
     <row r="607" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H607" s="6"/>
+      <c r="H607" s="2"/>
     </row>
     <row r="608" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H608" s="6"/>
+      <c r="H608" s="2"/>
     </row>
     <row r="609" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H609" s="6"/>
+      <c r="H609" s="2"/>
     </row>
     <row r="610" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H610" s="6"/>
+      <c r="H610" s="2"/>
     </row>
     <row r="611" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H611" s="6"/>
+      <c r="H611" s="2"/>
     </row>
     <row r="612" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H612" s="6"/>
+      <c r="H612" s="2"/>
     </row>
     <row r="613" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H613" s="6"/>
+      <c r="H613" s="2"/>
     </row>
     <row r="614" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H614" s="6"/>
+      <c r="H614" s="2"/>
     </row>
     <row r="615" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H615" s="6"/>
+      <c r="H615" s="2"/>
     </row>
     <row r="616" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H616" s="6"/>
+      <c r="H616" s="2"/>
     </row>
     <row r="617" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H617" s="6"/>
+      <c r="H617" s="2"/>
     </row>
     <row r="618" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H618" s="6"/>
+      <c r="H618" s="2"/>
     </row>
     <row r="619" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H619" s="6"/>
+      <c r="H619" s="2"/>
     </row>
     <row r="620" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H620" s="6"/>
+      <c r="H620" s="2"/>
     </row>
     <row r="621" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H621" s="6"/>
+      <c r="H621" s="2"/>
     </row>
     <row r="622" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H622" s="6"/>
+      <c r="H622" s="2"/>
     </row>
     <row r="623" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H623" s="6"/>
+      <c r="H623" s="2"/>
     </row>
     <row r="624" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H624" s="6"/>
+      <c r="H624" s="2"/>
     </row>
     <row r="625" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H625" s="6"/>
+      <c r="H625" s="2"/>
     </row>
     <row r="626" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H626" s="6"/>
+      <c r="H626" s="2"/>
     </row>
     <row r="627" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H627" s="6"/>
+      <c r="H627" s="2"/>
     </row>
     <row r="628" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H628" s="6"/>
+      <c r="H628" s="2"/>
     </row>
     <row r="629" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H629" s="6"/>
+      <c r="H629" s="2"/>
     </row>
     <row r="630" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H630" s="6"/>
+      <c r="H630" s="2"/>
     </row>
     <row r="631" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H631" s="6"/>
+      <c r="H631" s="2"/>
     </row>
     <row r="632" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H632" s="6"/>
+      <c r="H632" s="2"/>
     </row>
     <row r="633" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H633" s="6"/>
+      <c r="H633" s="2"/>
     </row>
     <row r="634" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H634" s="6"/>
+      <c r="H634" s="2"/>
     </row>
     <row r="635" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H635" s="6"/>
+      <c r="H635" s="2"/>
     </row>
     <row r="636" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H636" s="6"/>
+      <c r="H636" s="2"/>
     </row>
     <row r="637" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H637" s="6"/>
+      <c r="H637" s="2"/>
     </row>
     <row r="638" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H638" s="6"/>
+      <c r="H638" s="2"/>
     </row>
     <row r="639" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H639" s="6"/>
+      <c r="H639" s="2"/>
     </row>
     <row r="640" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H640" s="6"/>
+      <c r="H640" s="2"/>
     </row>
     <row r="641" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H641" s="6"/>
+      <c r="H641" s="2"/>
     </row>
     <row r="642" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H642" s="6"/>
+      <c r="H642" s="2"/>
     </row>
     <row r="643" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H643" s="6"/>
+      <c r="H643" s="2"/>
     </row>
     <row r="644" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H644" s="6"/>
+      <c r="H644" s="2"/>
     </row>
     <row r="645" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H645" s="6"/>
+      <c r="H645" s="2"/>
     </row>
     <row r="646" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H646" s="6"/>
+      <c r="H646" s="2"/>
     </row>
     <row r="647" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H647" s="6"/>
+      <c r="H647" s="2"/>
     </row>
     <row r="648" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H648" s="6"/>
+      <c r="H648" s="2"/>
     </row>
     <row r="649" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H649" s="6"/>
+      <c r="H649" s="2"/>
     </row>
     <row r="650" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H650" s="6"/>
+      <c r="H650" s="2"/>
     </row>
     <row r="651" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H651" s="6"/>
+      <c r="H651" s="2"/>
     </row>
     <row r="652" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H652" s="6"/>
+      <c r="H652" s="2"/>
     </row>
     <row r="653" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H653" s="6"/>
+      <c r="H653" s="2"/>
     </row>
     <row r="654" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H654" s="6"/>
+      <c r="H654" s="2"/>
     </row>
     <row r="655" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H655" s="6"/>
+      <c r="H655" s="2"/>
     </row>
     <row r="656" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H656" s="6"/>
+      <c r="H656" s="2"/>
     </row>
     <row r="657" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H657" s="6"/>
+      <c r="H657" s="2"/>
     </row>
     <row r="658" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H658" s="6"/>
+      <c r="H658" s="2"/>
     </row>
     <row r="659" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H659" s="6"/>
+      <c r="H659" s="2"/>
     </row>
     <row r="660" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H660" s="6"/>
+      <c r="H660" s="2"/>
     </row>
     <row r="661" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H661" s="6"/>
+      <c r="H661" s="2"/>
     </row>
     <row r="662" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H662" s="6"/>
+      <c r="H662" s="2"/>
     </row>
     <row r="663" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H663" s="6"/>
+      <c r="H663" s="2"/>
     </row>
     <row r="664" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H664" s="6"/>
+      <c r="H664" s="2"/>
     </row>
     <row r="665" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H665" s="6"/>
+      <c r="H665" s="2"/>
     </row>
     <row r="666" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H666" s="6"/>
+      <c r="H666" s="2"/>
     </row>
     <row r="667" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H667" s="6"/>
+      <c r="H667" s="2"/>
     </row>
     <row r="668" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H668" s="6"/>
+      <c r="H668" s="2"/>
     </row>
     <row r="669" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H669" s="6"/>
+      <c r="H669" s="2"/>
     </row>
     <row r="670" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H670" s="6"/>
+      <c r="H670" s="2"/>
     </row>
     <row r="671" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H671" s="6"/>
+      <c r="H671" s="2"/>
     </row>
     <row r="672" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H672" s="6"/>
+      <c r="H672" s="2"/>
     </row>
     <row r="673" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H673" s="6"/>
+      <c r="H673" s="2"/>
     </row>
     <row r="674" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H674" s="6"/>
+      <c r="H674" s="2"/>
     </row>
     <row r="675" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H675" s="6"/>
+      <c r="H675" s="2"/>
     </row>
     <row r="676" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H676" s="6"/>
+      <c r="H676" s="2"/>
     </row>
     <row r="677" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H677" s="6"/>
+      <c r="H677" s="2"/>
     </row>
     <row r="678" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H678" s="6"/>
+      <c r="H678" s="2"/>
     </row>
     <row r="679" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H679" s="6"/>
+      <c r="H679" s="2"/>
     </row>
     <row r="680" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H680" s="6"/>
+      <c r="H680" s="2"/>
     </row>
     <row r="681" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H681" s="6"/>
+      <c r="H681" s="2"/>
     </row>
     <row r="682" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H682" s="6"/>
+      <c r="H682" s="2"/>
     </row>
     <row r="683" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H683" s="6"/>
+      <c r="H683" s="2"/>
     </row>
     <row r="684" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H684" s="6"/>
+      <c r="H684" s="2"/>
     </row>
     <row r="685" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H685" s="6"/>
+      <c r="H685" s="2"/>
     </row>
     <row r="686" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H686" s="6"/>
+      <c r="H686" s="2"/>
     </row>
     <row r="687" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H687" s="6"/>
+      <c r="H687" s="2"/>
     </row>
     <row r="688" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H688" s="6"/>
+      <c r="H688" s="2"/>
     </row>
     <row r="689" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H689" s="6"/>
+      <c r="H689" s="2"/>
     </row>
     <row r="690" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H690" s="6"/>
+      <c r="H690" s="2"/>
     </row>
     <row r="691" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H691" s="6"/>
+      <c r="H691" s="2"/>
     </row>
     <row r="692" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H692" s="6"/>
+      <c r="H692" s="2"/>
     </row>
     <row r="693" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H693" s="6"/>
+      <c r="H693" s="2"/>
     </row>
     <row r="694" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H694" s="6"/>
+      <c r="H694" s="2"/>
     </row>
     <row r="695" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H695" s="6"/>
+      <c r="H695" s="2"/>
     </row>
     <row r="696" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H696" s="6"/>
+      <c r="H696" s="2"/>
     </row>
     <row r="697" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H697" s="6"/>
+      <c r="H697" s="2"/>
     </row>
     <row r="698" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H698" s="6"/>
+      <c r="H698" s="2"/>
     </row>
     <row r="699" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H699" s="6"/>
+      <c r="H699" s="2"/>
     </row>
     <row r="700" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H700" s="6"/>
+      <c r="H700" s="2"/>
     </row>
     <row r="701" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H701" s="6"/>
+      <c r="H701" s="2"/>
     </row>
     <row r="702" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H702" s="6"/>
+      <c r="H702" s="2"/>
     </row>
     <row r="703" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H703" s="6"/>
+      <c r="H703" s="2"/>
     </row>
     <row r="704" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H704" s="6"/>
+      <c r="H704" s="2"/>
     </row>
     <row r="705" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H705" s="6"/>
+      <c r="H705" s="2"/>
     </row>
     <row r="706" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H706" s="6"/>
+      <c r="H706" s="2"/>
     </row>
     <row r="707" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H707" s="6"/>
+      <c r="H707" s="2"/>
     </row>
     <row r="708" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H708" s="6"/>
+      <c r="H708" s="2"/>
     </row>
     <row r="709" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H709" s="6"/>
+      <c r="H709" s="2"/>
     </row>
     <row r="710" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H710" s="6"/>
+      <c r="H710" s="2"/>
     </row>
     <row r="711" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H711" s="6"/>
+      <c r="H711" s="2"/>
     </row>
     <row r="712" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H712" s="6"/>
+      <c r="H712" s="2"/>
     </row>
     <row r="713" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H713" s="6"/>
+      <c r="H713" s="2"/>
     </row>
     <row r="714" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H714" s="6"/>
+      <c r="H714" s="2"/>
     </row>
     <row r="715" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H715" s="6"/>
+      <c r="H715" s="2"/>
     </row>
     <row r="716" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H716" s="6"/>
+      <c r="H716" s="2"/>
     </row>
     <row r="717" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H717" s="6"/>
+      <c r="H717" s="2"/>
     </row>
     <row r="718" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H718" s="6"/>
+      <c r="H718" s="2"/>
     </row>
     <row r="719" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H719" s="6"/>
+      <c r="H719" s="2"/>
     </row>
     <row r="720" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H720" s="6"/>
+      <c r="H720" s="2"/>
     </row>
     <row r="721" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H721" s="6"/>
+      <c r="H721" s="2"/>
     </row>
     <row r="722" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H722" s="6"/>
+      <c r="H722" s="2"/>
     </row>
     <row r="723" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H723" s="6"/>
+      <c r="H723" s="2"/>
     </row>
     <row r="724" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H724" s="6"/>
+      <c r="H724" s="2"/>
     </row>
     <row r="725" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H725" s="6"/>
+      <c r="H725" s="2"/>
     </row>
     <row r="726" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H726" s="6"/>
+      <c r="H726" s="2"/>
     </row>
     <row r="727" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H727" s="6"/>
+      <c r="H727" s="2"/>
     </row>
     <row r="728" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H728" s="6"/>
+      <c r="H728" s="2"/>
     </row>
     <row r="729" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H729" s="6"/>
+      <c r="H729" s="2"/>
     </row>
     <row r="730" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H730" s="6"/>
+      <c r="H730" s="2"/>
     </row>
     <row r="731" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H731" s="6"/>
+      <c r="H731" s="2"/>
     </row>
     <row r="732" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H732" s="6"/>
+      <c r="H732" s="2"/>
     </row>
     <row r="733" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H733" s="6"/>
+      <c r="H733" s="2"/>
     </row>
     <row r="734" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H734" s="6"/>
+      <c r="H734" s="2"/>
     </row>
     <row r="735" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H735" s="6"/>
+      <c r="H735" s="2"/>
     </row>
     <row r="736" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H736" s="6"/>
+      <c r="H736" s="2"/>
     </row>
     <row r="737" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H737" s="6"/>
+      <c r="H737" s="2"/>
     </row>
     <row r="738" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H738" s="6"/>
+      <c r="H738" s="2"/>
     </row>
     <row r="739" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H739" s="6"/>
+      <c r="H739" s="2"/>
     </row>
     <row r="740" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H740" s="6"/>
+      <c r="H740" s="2"/>
     </row>
     <row r="741" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H741" s="6"/>
+      <c r="H741" s="2"/>
     </row>
     <row r="742" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H742" s="6"/>
+      <c r="H742" s="2"/>
     </row>
     <row r="743" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H743" s="6"/>
+      <c r="H743" s="2"/>
     </row>
     <row r="744" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H744" s="6"/>
+      <c r="H744" s="2"/>
     </row>
     <row r="745" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H745" s="6"/>
+      <c r="H745" s="2"/>
     </row>
     <row r="746" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H746" s="6"/>
+      <c r="H746" s="2"/>
     </row>
     <row r="747" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H747" s="6"/>
+      <c r="H747" s="2"/>
     </row>
     <row r="748" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H748" s="6"/>
+      <c r="H748" s="2"/>
     </row>
     <row r="749" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H749" s="6"/>
+      <c r="H749" s="2"/>
     </row>
     <row r="750" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H750" s="6"/>
+      <c r="H750" s="2"/>
     </row>
     <row r="751" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H751" s="6"/>
+      <c r="H751" s="2"/>
     </row>
     <row r="752" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H752" s="6"/>
+      <c r="H752" s="2"/>
     </row>
     <row r="753" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H753" s="6"/>
+      <c r="H753" s="2"/>
     </row>
     <row r="754" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H754" s="6"/>
+      <c r="H754" s="2"/>
     </row>
     <row r="755" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H755" s="6"/>
+      <c r="H755" s="2"/>
     </row>
     <row r="756" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H756" s="6"/>
+      <c r="H756" s="2"/>
     </row>
     <row r="757" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H757" s="6"/>
+      <c r="H757" s="2"/>
     </row>
     <row r="758" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H758" s="6"/>
+      <c r="H758" s="2"/>
     </row>
     <row r="759" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H759" s="6"/>
+      <c r="H759" s="2"/>
     </row>
     <row r="760" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H760" s="6"/>
+      <c r="H760" s="2"/>
     </row>
     <row r="761" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H761" s="6"/>
+      <c r="H761" s="2"/>
     </row>
     <row r="762" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H762" s="6"/>
+      <c r="H762" s="2"/>
     </row>
     <row r="763" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H763" s="6"/>
+      <c r="H763" s="2"/>
     </row>
     <row r="764" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H764" s="6"/>
+      <c r="H764" s="2"/>
     </row>
     <row r="765" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H765" s="6"/>
+      <c r="H765" s="2"/>
     </row>
     <row r="766" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H766" s="6"/>
+      <c r="H766" s="2"/>
     </row>
     <row r="767" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H767" s="6"/>
+      <c r="H767" s="2"/>
     </row>
     <row r="768" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H768" s="6"/>
+      <c r="H768" s="2"/>
     </row>
     <row r="769" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H769" s="6"/>
+      <c r="H769" s="2"/>
     </row>
     <row r="770" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H770" s="6"/>
+      <c r="H770" s="2"/>
     </row>
     <row r="771" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H771" s="6"/>
+      <c r="H771" s="2"/>
     </row>
     <row r="772" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H772" s="6"/>
+      <c r="H772" s="2"/>
     </row>
     <row r="773" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H773" s="6"/>
+      <c r="H773" s="2"/>
     </row>
     <row r="774" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H774" s="6"/>
+      <c r="H774" s="2"/>
     </row>
     <row r="775" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H775" s="6"/>
+      <c r="H775" s="2"/>
     </row>
     <row r="776" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H776" s="6"/>
+      <c r="H776" s="2"/>
     </row>
     <row r="777" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H777" s="6"/>
+      <c r="H777" s="2"/>
     </row>
     <row r="778" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H778" s="6"/>
+      <c r="H778" s="2"/>
     </row>
     <row r="779" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H779" s="6"/>
+      <c r="H779" s="2"/>
     </row>
     <row r="780" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H780" s="6"/>
+      <c r="H780" s="2"/>
     </row>
     <row r="781" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H781" s="6"/>
+      <c r="H781" s="2"/>
     </row>
     <row r="782" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H782" s="6"/>
+      <c r="H782" s="2"/>
     </row>
     <row r="783" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H783" s="6"/>
+      <c r="H783" s="2"/>
     </row>
     <row r="784" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H784" s="6"/>
+      <c r="H784" s="2"/>
     </row>
     <row r="785" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H785" s="6"/>
+      <c r="H785" s="2"/>
     </row>
     <row r="786" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H786" s="6"/>
+      <c r="H786" s="2"/>
     </row>
     <row r="787" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H787" s="6"/>
+      <c r="H787" s="2"/>
     </row>
     <row r="788" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H788" s="6"/>
+      <c r="H788" s="2"/>
     </row>
     <row r="789" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H789" s="6"/>
+      <c r="H789" s="2"/>
     </row>
     <row r="790" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H790" s="6"/>
+      <c r="H790" s="2"/>
     </row>
     <row r="791" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H791" s="6"/>
+      <c r="H791" s="2"/>
     </row>
     <row r="792" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H792" s="6"/>
+      <c r="H792" s="2"/>
     </row>
     <row r="793" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H793" s="6"/>
+      <c r="H793" s="2"/>
     </row>
     <row r="794" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H794" s="6"/>
+      <c r="H794" s="2"/>
     </row>
     <row r="795" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H795" s="6"/>
+      <c r="H795" s="2"/>
     </row>
     <row r="796" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H796" s="6"/>
+      <c r="H796" s="2"/>
     </row>
     <row r="797" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H797" s="6"/>
+      <c r="H797" s="2"/>
     </row>
     <row r="798" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H798" s="6"/>
+      <c r="H798" s="2"/>
     </row>
     <row r="799" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H799" s="6"/>
+      <c r="H799" s="2"/>
     </row>
     <row r="800" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H800" s="6"/>
+      <c r="H800" s="2"/>
     </row>
     <row r="801" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H801" s="6"/>
+      <c r="H801" s="2"/>
     </row>
     <row r="802" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H802" s="6"/>
+      <c r="H802" s="2"/>
     </row>
     <row r="803" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H803" s="6"/>
+      <c r="H803" s="2"/>
     </row>
     <row r="804" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H804" s="6"/>
+      <c r="H804" s="2"/>
     </row>
     <row r="805" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H805" s="6"/>
+      <c r="H805" s="2"/>
     </row>
     <row r="806" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H806" s="6"/>
+      <c r="H806" s="2"/>
     </row>
     <row r="807" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H807" s="6"/>
+      <c r="H807" s="2"/>
     </row>
     <row r="808" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H808" s="6"/>
+      <c r="H808" s="2"/>
     </row>
     <row r="809" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H809" s="6"/>
+      <c r="H809" s="2"/>
     </row>
     <row r="810" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H810" s="6"/>
+      <c r="H810" s="2"/>
     </row>
     <row r="811" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H811" s="6"/>
+      <c r="H811" s="2"/>
     </row>
     <row r="812" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H812" s="6"/>
+      <c r="H812" s="2"/>
     </row>
     <row r="813" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H813" s="6"/>
+      <c r="H813" s="2"/>
     </row>
     <row r="814" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H814" s="6"/>
+      <c r="H814" s="2"/>
     </row>
     <row r="815" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H815" s="6"/>
+      <c r="H815" s="2"/>
     </row>
     <row r="816" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H816" s="6"/>
+      <c r="H816" s="2"/>
     </row>
     <row r="817" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H817" s="6"/>
+      <c r="H817" s="2"/>
     </row>
     <row r="818" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H818" s="6"/>
+      <c r="H818" s="2"/>
     </row>
     <row r="819" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H819" s="6"/>
+      <c r="H819" s="2"/>
     </row>
     <row r="820" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H820" s="6"/>
+      <c r="H820" s="2"/>
     </row>
     <row r="821" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H821" s="6"/>
+      <c r="H821" s="2"/>
     </row>
     <row r="822" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H822" s="6"/>
+      <c r="H822" s="2"/>
     </row>
     <row r="823" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H823" s="6"/>
+      <c r="H823" s="2"/>
     </row>
     <row r="824" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H824" s="6"/>
+      <c r="H824" s="2"/>
     </row>
     <row r="825" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H825" s="6"/>
+      <c r="H825" s="2"/>
     </row>
     <row r="826" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H826" s="6"/>
+      <c r="H826" s="2"/>
     </row>
     <row r="827" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H827" s="6"/>
+      <c r="H827" s="2"/>
     </row>
     <row r="828" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H828" s="6"/>
+      <c r="H828" s="2"/>
     </row>
     <row r="829" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H829" s="6"/>
+      <c r="H829" s="2"/>
     </row>
     <row r="830" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H830" s="6"/>
+      <c r="H830" s="2"/>
     </row>
     <row r="831" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H831" s="6"/>
+      <c r="H831" s="2"/>
     </row>
     <row r="832" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H832" s="6"/>
+      <c r="H832" s="2"/>
     </row>
     <row r="833" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H833" s="6"/>
+      <c r="H833" s="2"/>
     </row>
     <row r="834" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H834" s="6"/>
+      <c r="H834" s="2"/>
     </row>
     <row r="835" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H835" s="6"/>
+      <c r="H835" s="2"/>
     </row>
     <row r="836" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H836" s="6"/>
+      <c r="H836" s="2"/>
     </row>
     <row r="837" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H837" s="6"/>
+      <c r="H837" s="2"/>
     </row>
     <row r="838" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H838" s="6"/>
+      <c r="H838" s="2"/>
     </row>
     <row r="839" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H839" s="6"/>
+      <c r="H839" s="2"/>
     </row>
     <row r="840" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H840" s="6"/>
+      <c r="H840" s="2"/>
     </row>
     <row r="841" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H841" s="6"/>
+      <c r="H841" s="2"/>
     </row>
     <row r="842" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H842" s="6"/>
+      <c r="H842" s="2"/>
     </row>
     <row r="843" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H843" s="6"/>
+      <c r="H843" s="2"/>
     </row>
     <row r="844" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H844" s="6"/>
+      <c r="H844" s="2"/>
     </row>
     <row r="845" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H845" s="6"/>
+      <c r="H845" s="2"/>
     </row>
     <row r="846" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H846" s="6"/>
+      <c r="H846" s="2"/>
     </row>
     <row r="847" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H847" s="6"/>
+      <c r="H847" s="2"/>
     </row>
     <row r="848" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H848" s="6"/>
+      <c r="H848" s="2"/>
     </row>
     <row r="849" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H849" s="6"/>
+      <c r="H849" s="2"/>
     </row>
     <row r="850" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H850" s="6"/>
+      <c r="H850" s="2"/>
     </row>
     <row r="851" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H851" s="6"/>
+      <c r="H851" s="2"/>
     </row>
     <row r="852" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H852" s="6"/>
+      <c r="H852" s="2"/>
     </row>
     <row r="853" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H853" s="6"/>
+      <c r="H853" s="2"/>
     </row>
     <row r="854" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H854" s="6"/>
+      <c r="H854" s="2"/>
     </row>
     <row r="855" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H855" s="6"/>
+      <c r="H855" s="2"/>
     </row>
     <row r="856" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H856" s="6"/>
+      <c r="H856" s="2"/>
     </row>
     <row r="857" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H857" s="6"/>
+      <c r="H857" s="2"/>
     </row>
     <row r="858" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H858" s="6"/>
+      <c r="H858" s="2"/>
     </row>
     <row r="859" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H859" s="6"/>
+      <c r="H859" s="2"/>
     </row>
     <row r="860" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H860" s="6"/>
+      <c r="H860" s="2"/>
     </row>
     <row r="861" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H861" s="6"/>
+      <c r="H861" s="2"/>
     </row>
     <row r="862" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H862" s="6"/>
+      <c r="H862" s="2"/>
     </row>
     <row r="863" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H863" s="6"/>
+      <c r="H863" s="2"/>
     </row>
     <row r="864" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H864" s="6"/>
+      <c r="H864" s="2"/>
     </row>
     <row r="865" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H865" s="6"/>
+      <c r="H865" s="2"/>
     </row>
     <row r="866" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H866" s="6"/>
+      <c r="H866" s="2"/>
     </row>
     <row r="867" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H867" s="6"/>
+      <c r="H867" s="2"/>
     </row>
     <row r="868" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H868" s="6"/>
+      <c r="H868" s="2"/>
     </row>
     <row r="869" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H869" s="6"/>
+      <c r="H869" s="2"/>
     </row>
     <row r="870" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H870" s="6"/>
+      <c r="H870" s="2"/>
     </row>
     <row r="871" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H871" s="6"/>
+      <c r="H871" s="2"/>
     </row>
     <row r="872" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H872" s="6"/>
+      <c r="H872" s="2"/>
     </row>
     <row r="873" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H873" s="6"/>
+      <c r="H873" s="2"/>
     </row>
     <row r="874" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H874" s="6"/>
+      <c r="H874" s="2"/>
     </row>
     <row r="875" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H875" s="6"/>
+      <c r="H875" s="2"/>
     </row>
     <row r="876" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H876" s="6"/>
+      <c r="H876" s="2"/>
     </row>
     <row r="877" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H877" s="6"/>
+      <c r="H877" s="2"/>
     </row>
     <row r="878" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H878" s="6"/>
+      <c r="H878" s="2"/>
     </row>
     <row r="879" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H879" s="6"/>
+      <c r="H879" s="2"/>
     </row>
     <row r="880" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H880" s="6"/>
+      <c r="H880" s="2"/>
     </row>
     <row r="881" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H881" s="6"/>
+      <c r="H881" s="2"/>
     </row>
     <row r="882" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H882" s="6"/>
+      <c r="H882" s="2"/>
     </row>
     <row r="883" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H883" s="6"/>
+      <c r="H883" s="2"/>
     </row>
     <row r="884" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H884" s="6"/>
+      <c r="H884" s="2"/>
     </row>
     <row r="885" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H885" s="6"/>
+      <c r="H885" s="2"/>
     </row>
     <row r="886" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H886" s="6"/>
+      <c r="H886" s="2"/>
     </row>
     <row r="887" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H887" s="6"/>
+      <c r="H887" s="2"/>
     </row>
     <row r="888" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H888" s="6"/>
+      <c r="H888" s="2"/>
     </row>
     <row r="889" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H889" s="6"/>
+      <c r="H889" s="2"/>
     </row>
     <row r="890" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H890" s="6"/>
+      <c r="H890" s="2"/>
     </row>
     <row r="891" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H891" s="6"/>
+      <c r="H891" s="2"/>
     </row>
     <row r="892" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H892" s="6"/>
+      <c r="H892" s="2"/>
     </row>
     <row r="893" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H893" s="6"/>
+      <c r="H893" s="2"/>
     </row>
     <row r="894" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H894" s="6"/>
+      <c r="H894" s="2"/>
     </row>
     <row r="895" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H895" s="6"/>
+      <c r="H895" s="2"/>
     </row>
     <row r="896" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H896" s="6"/>
+      <c r="H896" s="2"/>
     </row>
     <row r="897" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H897" s="6"/>
+      <c r="H897" s="2"/>
     </row>
     <row r="898" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H898" s="6"/>
+      <c r="H898" s="2"/>
     </row>
     <row r="899" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H899" s="6"/>
+      <c r="H899" s="2"/>
     </row>
     <row r="900" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H900" s="6"/>
+      <c r="H900" s="2"/>
     </row>
     <row r="901" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H901" s="6"/>
+      <c r="H901" s="2"/>
     </row>
     <row r="902" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H902" s="6"/>
+      <c r="H902" s="2"/>
     </row>
     <row r="903" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H903" s="6"/>
+      <c r="H903" s="2"/>
     </row>
     <row r="904" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H904" s="6"/>
+      <c r="H904" s="2"/>
     </row>
     <row r="905" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H905" s="6"/>
+      <c r="H905" s="2"/>
     </row>
     <row r="906" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H906" s="6"/>
+      <c r="H906" s="2"/>
     </row>
     <row r="907" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H907" s="6"/>
+      <c r="H907" s="2"/>
     </row>
     <row r="908" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H908" s="6"/>
+      <c r="H908" s="2"/>
     </row>
     <row r="909" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H909" s="6"/>
+      <c r="H909" s="2"/>
     </row>
     <row r="910" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H910" s="6"/>
+      <c r="H910" s="2"/>
     </row>
     <row r="911" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H911" s="6"/>
+      <c r="H911" s="2"/>
     </row>
     <row r="912" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H912" s="6"/>
+      <c r="H912" s="2"/>
     </row>
     <row r="913" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H913" s="6"/>
+      <c r="H913" s="2"/>
     </row>
     <row r="914" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H914" s="6"/>
+      <c r="H914" s="2"/>
     </row>
     <row r="915" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H915" s="6"/>
+      <c r="H915" s="2"/>
     </row>
     <row r="916" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H916" s="6"/>
+      <c r="H916" s="2"/>
     </row>
     <row r="917" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H917" s="6"/>
+      <c r="H917" s="2"/>
     </row>
     <row r="918" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H918" s="6"/>
+      <c r="H918" s="2"/>
     </row>
     <row r="919" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H919" s="6"/>
+      <c r="H919" s="2"/>
     </row>
     <row r="920" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H920" s="6"/>
+      <c r="H920" s="2"/>
     </row>
     <row r="921" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H921" s="6"/>
+      <c r="H921" s="2"/>
     </row>
     <row r="922" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H922" s="6"/>
+      <c r="H922" s="2"/>
     </row>
     <row r="923" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H923" s="6"/>
+      <c r="H923" s="2"/>
     </row>
     <row r="924" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H924" s="6"/>
+      <c r="H924" s="2"/>
     </row>
     <row r="925" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H925" s="6"/>
+      <c r="H925" s="2"/>
     </row>
     <row r="926" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H926" s="6"/>
+      <c r="H926" s="2"/>
     </row>
     <row r="927" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H927" s="6"/>
+      <c r="H927" s="2"/>
     </row>
     <row r="928" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H928" s="6"/>
+      <c r="H928" s="2"/>
     </row>
     <row r="929" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H929" s="6"/>
+      <c r="H929" s="2"/>
     </row>
     <row r="930" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H930" s="6"/>
+      <c r="H930" s="2"/>
     </row>
     <row r="931" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H931" s="6"/>
+      <c r="H931" s="2"/>
     </row>
     <row r="932" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H932" s="6"/>
+      <c r="H932" s="2"/>
     </row>
     <row r="933" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H933" s="6"/>
+      <c r="H933" s="2"/>
     </row>
     <row r="934" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H934" s="6"/>
+      <c r="H934" s="2"/>
     </row>
     <row r="935" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H935" s="6"/>
+      <c r="H935" s="2"/>
     </row>
     <row r="936" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H936" s="6"/>
+      <c r="H936" s="2"/>
     </row>
     <row r="937" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H937" s="6"/>
+      <c r="H937" s="2"/>
     </row>
     <row r="938" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H938" s="6"/>
+      <c r="H938" s="2"/>
     </row>
     <row r="939" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H939" s="6"/>
+      <c r="H939" s="2"/>
     </row>
     <row r="940" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H940" s="6"/>
+      <c r="H940" s="2"/>
     </row>
     <row r="941" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H941" s="6"/>
+      <c r="H941" s="2"/>
     </row>
     <row r="942" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H942" s="6"/>
+      <c r="H942" s="2"/>
     </row>
     <row r="943" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H943" s="6"/>
+      <c r="H943" s="2"/>
     </row>
     <row r="944" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H944" s="6"/>
+      <c r="H944" s="2"/>
     </row>
     <row r="945" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H945" s="6"/>
+      <c r="H945" s="2"/>
     </row>
     <row r="946" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H946" s="6"/>
+      <c r="H946" s="2"/>
     </row>
     <row r="947" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H947" s="6"/>
+      <c r="H947" s="2"/>
     </row>
     <row r="948" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H948" s="6"/>
+      <c r="H948" s="2"/>
     </row>
     <row r="949" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H949" s="6"/>
+      <c r="H949" s="2"/>
     </row>
     <row r="950" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H950" s="6"/>
+      <c r="H950" s="2"/>
     </row>
     <row r="951" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H951" s="6"/>
+      <c r="H951" s="2"/>
     </row>
     <row r="952" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H952" s="6"/>
+      <c r="H952" s="2"/>
     </row>
     <row r="953" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H953" s="6"/>
+      <c r="H953" s="2"/>
     </row>
     <row r="954" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H954" s="6"/>
+      <c r="H954" s="2"/>
     </row>
     <row r="955" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H955" s="6"/>
+      <c r="H955" s="2"/>
     </row>
     <row r="956" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H956" s="6"/>
+      <c r="H956" s="2"/>
     </row>
     <row r="957" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H957" s="6"/>
+      <c r="H957" s="2"/>
     </row>
     <row r="958" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H958" s="6"/>
+      <c r="H958" s="2"/>
     </row>
     <row r="959" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H959" s="6"/>
+      <c r="H959" s="2"/>
     </row>
     <row r="960" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H960" s="6"/>
+      <c r="H960" s="2"/>
     </row>
     <row r="961" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H961" s="6"/>
+      <c r="H961" s="2"/>
     </row>
     <row r="962" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H962" s="6"/>
+      <c r="H962" s="2"/>
     </row>
     <row r="963" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H963" s="6"/>
+      <c r="H963" s="2"/>
     </row>
     <row r="964" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H964" s="6"/>
+      <c r="H964" s="2"/>
     </row>
     <row r="965" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H965" s="6"/>
+      <c r="H965" s="2"/>
     </row>
     <row r="966" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H966" s="6"/>
+      <c r="H966" s="2"/>
     </row>
     <row r="967" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H967" s="6"/>
+      <c r="H967" s="2"/>
     </row>
     <row r="968" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H968" s="6"/>
+      <c r="H968" s="2"/>
     </row>
     <row r="969" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H969" s="6"/>
+      <c r="H969" s="2"/>
     </row>
     <row r="970" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H970" s="6"/>
+      <c r="H970" s="2"/>
     </row>
     <row r="971" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H971" s="6"/>
+      <c r="H971" s="2"/>
     </row>
     <row r="972" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H972" s="6"/>
+      <c r="H972" s="2"/>
     </row>
     <row r="973" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H973" s="6"/>
+      <c r="H973" s="2"/>
     </row>
     <row r="974" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H974" s="6"/>
+      <c r="H974" s="2"/>
     </row>
     <row r="975" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H975" s="6"/>
+      <c r="H975" s="2"/>
     </row>
     <row r="976" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H976" s="6"/>
+      <c r="H976" s="2"/>
     </row>
     <row r="977" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H977" s="6"/>
+      <c r="H977" s="2"/>
     </row>
     <row r="978" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H978" s="6"/>
+      <c r="H978" s="2"/>
     </row>
     <row r="979" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H979" s="6"/>
+      <c r="H979" s="2"/>
     </row>
     <row r="980" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H980" s="6"/>
+      <c r="H980" s="2"/>
     </row>
     <row r="981" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H981" s="6"/>
+      <c r="H981" s="2"/>
     </row>
     <row r="982" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H982" s="6"/>
+      <c r="H982" s="2"/>
     </row>
     <row r="983" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H983" s="6"/>
+      <c r="H983" s="2"/>
     </row>
     <row r="984" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H984" s="6"/>
+      <c r="H984" s="2"/>
     </row>
     <row r="985" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H985" s="6"/>
+      <c r="H985" s="2"/>
     </row>
     <row r="986" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H986" s="6"/>
+      <c r="H986" s="2"/>
     </row>
     <row r="987" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H987" s="6"/>
+      <c r="H987" s="2"/>
     </row>
     <row r="988" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H988" s="6"/>
+      <c r="H988" s="2"/>
     </row>
     <row r="989" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H989" s="6"/>
+      <c r="H989" s="2"/>
     </row>
     <row r="990" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H990" s="6"/>
+      <c r="H990" s="2"/>
     </row>
     <row r="991" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H991" s="6"/>
+      <c r="H991" s="2"/>
     </row>
     <row r="992" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H992" s="6"/>
+      <c r="H992" s="2"/>
     </row>
     <row r="993" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H993" s="6"/>
+      <c r="H993" s="2"/>
     </row>
     <row r="994" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H994" s="6"/>
+      <c r="H994" s="2"/>
     </row>
     <row r="995" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H995" s="6"/>
+      <c r="H995" s="2"/>
     </row>
     <row r="996" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H996" s="6"/>
+      <c r="H996" s="2"/>
     </row>
     <row r="997" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H997" s="6"/>
+      <c r="H997" s="2"/>
     </row>
     <row r="998" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H998" s="6"/>
+      <c r="H998" s="2"/>
     </row>
     <row r="999" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H999" s="6"/>
+      <c r="H999" s="2"/>
     </row>
     <row r="1000" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="H1000" s="6"/>
+      <c r="H1000" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/template/Template_perizinan Proyek.xlsx
+++ b/template/Template_perizinan Proyek.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvin\Documents\Coolyeah\PKT\Inventor\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E388ECFA-940D-4351-BCB4-FD672D552450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F39042-12D7-49DF-8C92-5988E10CD136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perizinan proyek" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="93">
   <si>
     <t>Penanggung Jawab</t>
   </si>
@@ -43,480 +44,12 @@
     <t>Tgl Expired</t>
   </si>
   <si>
-    <t>Overhead Crane 1 Ton</t>
-  </si>
-  <si>
-    <t>Aset Peralatan</t>
-  </si>
-  <si>
-    <t>CR-001</t>
-  </si>
-  <si>
-    <t>Bay 1</t>
-  </si>
-  <si>
-    <t>Dept Pemeliharaan</t>
-  </si>
-  <si>
-    <t>Sertifikat Layak Operasi</t>
-  </si>
-  <si>
-    <t>SLO-CR001</t>
-  </si>
-  <si>
     <t>Sertifikat K3</t>
   </si>
   <si>
-    <t>K3-CR001</t>
-  </si>
-  <si>
-    <t>Overhead Crane 2 Ton</t>
-  </si>
-  <si>
-    <t>CR-002</t>
-  </si>
-  <si>
-    <t>Bay 2</t>
-  </si>
-  <si>
-    <t>SLO-CR002</t>
-  </si>
-  <si>
-    <t>K3-CR002</t>
-  </si>
-  <si>
-    <t>Overhead Crane 3 Ton</t>
-  </si>
-  <si>
-    <t>CR-003</t>
-  </si>
-  <si>
-    <t>Bay 3</t>
-  </si>
-  <si>
-    <t>SLO-CR003</t>
-  </si>
-  <si>
-    <t>K3-CR003</t>
-  </si>
-  <si>
-    <t>Overhead Crane 4 Ton</t>
-  </si>
-  <si>
-    <t>CR-004</t>
-  </si>
-  <si>
-    <t>Bay 4</t>
-  </si>
-  <si>
-    <t>SLO-CR004</t>
-  </si>
-  <si>
-    <t>K3-CR004</t>
-  </si>
-  <si>
-    <t>Overhead Crane 5 Ton</t>
-  </si>
-  <si>
-    <t>CR-005</t>
-  </si>
-  <si>
-    <t>Bay 5</t>
-  </si>
-  <si>
-    <t>SLO-CR005</t>
-  </si>
-  <si>
-    <t>K3-CR005</t>
-  </si>
-  <si>
-    <t>Overhead Crane 6 Ton</t>
-  </si>
-  <si>
-    <t>CR-006</t>
-  </si>
-  <si>
-    <t>Bay 6</t>
-  </si>
-  <si>
-    <t>SLO-CR006</t>
-  </si>
-  <si>
-    <t>K3-CR006</t>
-  </si>
-  <si>
-    <t>Overhead Crane 7 Ton</t>
-  </si>
-  <si>
-    <t>CR-007</t>
-  </si>
-  <si>
-    <t>Bay 7</t>
-  </si>
-  <si>
-    <t>SLO-CR007</t>
-  </si>
-  <si>
-    <t>K3-CR007</t>
-  </si>
-  <si>
-    <t>Overhead Crane 8 Ton</t>
-  </si>
-  <si>
-    <t>CR-008</t>
-  </si>
-  <si>
-    <t>Bay 8</t>
-  </si>
-  <si>
-    <t>SLO-CR008</t>
-  </si>
-  <si>
-    <t>K3-CR008</t>
-  </si>
-  <si>
-    <t>Overhead Crane 9 Ton</t>
-  </si>
-  <si>
-    <t>CR-009</t>
-  </si>
-  <si>
-    <t>Bay 9</t>
-  </si>
-  <si>
-    <t>SLO-CR009</t>
-  </si>
-  <si>
-    <t>K3-CR009</t>
-  </si>
-  <si>
-    <t>Overhead Crane 10 Ton</t>
-  </si>
-  <si>
-    <t>CR-010</t>
-  </si>
-  <si>
-    <t>Bay 10</t>
-  </si>
-  <si>
-    <t>SLO-CR010</t>
-  </si>
-  <si>
-    <t>K3-CR010</t>
-  </si>
-  <si>
-    <t>Forklift 1 Ton</t>
-  </si>
-  <si>
-    <t>Aset Kendaraan</t>
-  </si>
-  <si>
-    <t>FL-001</t>
-  </si>
-  <si>
-    <t>Gudang 1</t>
-  </si>
-  <si>
     <t>Dept Logistik</t>
   </si>
   <si>
-    <t>SLO-FL001</t>
-  </si>
-  <si>
-    <t>K3-FL001</t>
-  </si>
-  <si>
-    <t>Forklift 2 Ton</t>
-  </si>
-  <si>
-    <t>FL-002</t>
-  </si>
-  <si>
-    <t>Gudang 2</t>
-  </si>
-  <si>
-    <t>SLO-FL002</t>
-  </si>
-  <si>
-    <t>K3-FL002</t>
-  </si>
-  <si>
-    <t>Forklift 3 Ton</t>
-  </si>
-  <si>
-    <t>FL-003</t>
-  </si>
-  <si>
-    <t>Gudang 3</t>
-  </si>
-  <si>
-    <t>SLO-FL003</t>
-  </si>
-  <si>
-    <t>K3-FL003</t>
-  </si>
-  <si>
-    <t>Forklift 4 Ton</t>
-  </si>
-  <si>
-    <t>FL-004</t>
-  </si>
-  <si>
-    <t>Gudang 4</t>
-  </si>
-  <si>
-    <t>SLO-FL004</t>
-  </si>
-  <si>
-    <t>K3-FL004</t>
-  </si>
-  <si>
-    <t>Forklift 5 Ton</t>
-  </si>
-  <si>
-    <t>FL-005</t>
-  </si>
-  <si>
-    <t>Gudang 5</t>
-  </si>
-  <si>
-    <t>SLO-FL005</t>
-  </si>
-  <si>
-    <t>K3-FL005</t>
-  </si>
-  <si>
-    <t>Forklift 6 Ton</t>
-  </si>
-  <si>
-    <t>FL-006</t>
-  </si>
-  <si>
-    <t>Gudang 6</t>
-  </si>
-  <si>
-    <t>SLO-FL006</t>
-  </si>
-  <si>
-    <t>K3-FL006</t>
-  </si>
-  <si>
-    <t>Forklift 7 Ton</t>
-  </si>
-  <si>
-    <t>FL-007</t>
-  </si>
-  <si>
-    <t>Gudang 7</t>
-  </si>
-  <si>
-    <t>SLO-FL007</t>
-  </si>
-  <si>
-    <t>K3-FL007</t>
-  </si>
-  <si>
-    <t>Forklift 8 Ton</t>
-  </si>
-  <si>
-    <t>FL-008</t>
-  </si>
-  <si>
-    <t>Gudang 8</t>
-  </si>
-  <si>
-    <t>SLO-FL008</t>
-  </si>
-  <si>
-    <t>K3-FL008</t>
-  </si>
-  <si>
-    <t>Forklift 9 Ton</t>
-  </si>
-  <si>
-    <t>FL-009</t>
-  </si>
-  <si>
-    <t>Gudang 9</t>
-  </si>
-  <si>
-    <t>SLO-FL009</t>
-  </si>
-  <si>
-    <t>K3-FL009</t>
-  </si>
-  <si>
-    <t>Forklift 10 Ton</t>
-  </si>
-  <si>
-    <t>FL-010</t>
-  </si>
-  <si>
-    <t>Gudang 10</t>
-  </si>
-  <si>
-    <t>SLO-FL010</t>
-  </si>
-  <si>
-    <t>K3-FL010</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 1</t>
-  </si>
-  <si>
-    <t>Mesin Produksi</t>
-  </si>
-  <si>
-    <t>KP-001</t>
-  </si>
-  <si>
-    <t>Pabrik 1</t>
-  </si>
-  <si>
-    <t>Dept Produksi</t>
-  </si>
-  <si>
-    <t>Sertifikat Tekanan Tinggi</t>
-  </si>
-  <si>
-    <t>STT-KP001</t>
-  </si>
-  <si>
-    <t>K3-KP001</t>
-  </si>
-  <si>
-    <t>KP-002</t>
-  </si>
-  <si>
-    <t>Pabrik 2</t>
-  </si>
-  <si>
-    <t>STT-KP002</t>
-  </si>
-  <si>
-    <t>K3-KP002</t>
-  </si>
-  <si>
-    <t>KP-003</t>
-  </si>
-  <si>
-    <t>Pabrik 3</t>
-  </si>
-  <si>
-    <t>STT-KP003</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 3</t>
-  </si>
-  <si>
-    <t>K3-KP003</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 4</t>
-  </si>
-  <si>
-    <t>KP-004</t>
-  </si>
-  <si>
-    <t>Pabrik 4</t>
-  </si>
-  <si>
-    <t>STT-KP004</t>
-  </si>
-  <si>
-    <t>K3-KP004</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 5</t>
-  </si>
-  <si>
-    <t>KP-005</t>
-  </si>
-  <si>
-    <t>Pabrik 5</t>
-  </si>
-  <si>
-    <t>STT-KP005</t>
-  </si>
-  <si>
-    <t>K3-KP005</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 6</t>
-  </si>
-  <si>
-    <t>KP-006</t>
-  </si>
-  <si>
-    <t>Pabrik 6</t>
-  </si>
-  <si>
-    <t>STT-KP006</t>
-  </si>
-  <si>
-    <t>K3-KP006</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 7</t>
-  </si>
-  <si>
-    <t>KP-007</t>
-  </si>
-  <si>
-    <t>Pabrik 7</t>
-  </si>
-  <si>
-    <t>STT-KP007</t>
-  </si>
-  <si>
-    <t>K3-KP007</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 8</t>
-  </si>
-  <si>
-    <t>KP-008</t>
-  </si>
-  <si>
-    <t>Pabrik 8</t>
-  </si>
-  <si>
-    <t>STT-KP008</t>
-  </si>
-  <si>
-    <t>K3-KP008</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 9</t>
-  </si>
-  <si>
-    <t>KP-009</t>
-  </si>
-  <si>
-    <t>Pabrik 9</t>
-  </si>
-  <si>
-    <t>STT-KP009</t>
-  </si>
-  <si>
-    <t>K3-KP009</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 10</t>
-  </si>
-  <si>
-    <t>KP-010</t>
-  </si>
-  <si>
-    <t>Pabrik 10</t>
-  </si>
-  <si>
-    <t>STT-KP010</t>
-  </si>
-  <si>
-    <t>K3-KP010</t>
-  </si>
-  <si>
     <t>Nama Proyek / Master (Wajib)</t>
   </si>
   <si>
@@ -527,13 +60,253 @@
   </si>
   <si>
     <t>Lokasi proyek</t>
+  </si>
+  <si>
+    <t>Jenis Proyek (Master)</t>
+  </si>
+  <si>
+    <t>Lokasi Proyek</t>
+  </si>
+  <si>
+    <t>Proyek Soda Ash</t>
+  </si>
+  <si>
+    <t>Proyek Pembangunan</t>
+  </si>
+  <si>
+    <t>PRJ-001</t>
+  </si>
+  <si>
+    <t>Area Pabrik Utama</t>
+  </si>
+  <si>
+    <t>Dept Project</t>
+  </si>
+  <si>
+    <t>Persetujuan Lingkungan</t>
+  </si>
+  <si>
+    <t>PL-PRJ001</t>
+  </si>
+  <si>
+    <t>Persetujuan Bangunan Gedung</t>
+  </si>
+  <si>
+    <t>PBG-PRJ001</t>
+  </si>
+  <si>
+    <t>Sertifikat Laik Fungsi</t>
+  </si>
+  <si>
+    <t>SLF-PRJ001</t>
+  </si>
+  <si>
+    <t>Proyek Pembangunan Dermaga</t>
+  </si>
+  <si>
+    <t>Proyek Infrastruktur</t>
+  </si>
+  <si>
+    <t>PRJ-002</t>
+  </si>
+  <si>
+    <t>Area Dermaga</t>
+  </si>
+  <si>
+    <t>Dept Engineering</t>
+  </si>
+  <si>
+    <t>PL-PRJ002</t>
+  </si>
+  <si>
+    <t>PBG-PRJ002</t>
+  </si>
+  <si>
+    <t>Izin Pembangunan Dermaga</t>
+  </si>
+  <si>
+    <t>IPD-PRJ002</t>
+  </si>
+  <si>
+    <t>Proyek Pipa Gas</t>
+  </si>
+  <si>
+    <t>PRJ-003</t>
+  </si>
+  <si>
+    <t>Jalur Pipa Gas</t>
+  </si>
+  <si>
+    <t>Izin Penggunaan Jalur Pipa</t>
+  </si>
+  <si>
+    <t>IPJP-PRJ003</t>
+  </si>
+  <si>
+    <t>PL-PRJ003</t>
+  </si>
+  <si>
+    <t>Sertifikat Kelayakan Operasi</t>
+  </si>
+  <si>
+    <t>SKO-PRJ003</t>
+  </si>
+  <si>
+    <t>Proyek Tank Farm</t>
+  </si>
+  <si>
+    <t>Proyek Fasilitas</t>
+  </si>
+  <si>
+    <t>PRJ-004</t>
+  </si>
+  <si>
+    <t>Area Tank Farm</t>
+  </si>
+  <si>
+    <t>PL-PRJ004</t>
+  </si>
+  <si>
+    <t>PBG-PRJ004</t>
+  </si>
+  <si>
+    <t>SLF-PRJ004</t>
+  </si>
+  <si>
+    <t>Proyek Instalasi Boiler</t>
+  </si>
+  <si>
+    <t>Proyek Utilitas</t>
+  </si>
+  <si>
+    <t>PRJ-005</t>
+  </si>
+  <si>
+    <t>Area Utility</t>
+  </si>
+  <si>
+    <t>Dept Maintenance</t>
+  </si>
+  <si>
+    <t>PL-PRJ005</t>
+  </si>
+  <si>
+    <t>SKO-PRJ005</t>
+  </si>
+  <si>
+    <t>K3-PRJ005</t>
+  </si>
+  <si>
+    <t>Proyek Pembangunan Gudang Bahan Baku</t>
+  </si>
+  <si>
+    <t>PRJ-006</t>
+  </si>
+  <si>
+    <t>Area Gudang</t>
+  </si>
+  <si>
+    <t>PBG-PRJ006</t>
+  </si>
+  <si>
+    <t>SLF-PRJ006</t>
+  </si>
+  <si>
+    <t>PL-PRJ006</t>
+  </si>
+  <si>
+    <t>Proyek Instalasi Conveyor</t>
+  </si>
+  <si>
+    <t>Proyek Peralatan</t>
+  </si>
+  <si>
+    <t>PRJ-007</t>
+  </si>
+  <si>
+    <t>Area Produksi</t>
+  </si>
+  <si>
+    <t>SKO-PRJ007</t>
+  </si>
+  <si>
+    <t>K3-PRJ007</t>
+  </si>
+  <si>
+    <t>Proyek Pengembangan Terminal BBM</t>
+  </si>
+  <si>
+    <t>PRJ-008</t>
+  </si>
+  <si>
+    <t>Area Terminal BBM</t>
+  </si>
+  <si>
+    <t>Dept Operasional</t>
+  </si>
+  <si>
+    <t>PL-PRJ008</t>
+  </si>
+  <si>
+    <t>Izin Operasional Terminal</t>
+  </si>
+  <si>
+    <t>IOT-PRJ008</t>
+  </si>
+  <si>
+    <t>SLF-PRJ008</t>
+  </si>
+  <si>
+    <t>Proyek Pembangunan Pembangkit Listrik</t>
+  </si>
+  <si>
+    <t>Proyek Energi</t>
+  </si>
+  <si>
+    <t>PRJ-009</t>
+  </si>
+  <si>
+    <t>Area Power Plant</t>
+  </si>
+  <si>
+    <t>PL-PRJ009</t>
+  </si>
+  <si>
+    <t>Sertifikat Laik Operasi</t>
+  </si>
+  <si>
+    <t>SLO-PRJ009</t>
+  </si>
+  <si>
+    <t>K3-PRJ009</t>
+  </si>
+  <si>
+    <t>Proyek Revitalisasi Kilang</t>
+  </si>
+  <si>
+    <t>Proyek Revitalisasi</t>
+  </si>
+  <si>
+    <t>PRJ-010</t>
+  </si>
+  <si>
+    <t>Area Kilang</t>
+  </si>
+  <si>
+    <t>PL-PRJ010</t>
+  </si>
+  <si>
+    <t>PBG-PRJ010</t>
+  </si>
+  <si>
+    <t>SLF-PRJ010</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -548,6 +321,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -572,13 +352,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,24 +592,25 @@
     <col min="1" max="1" width="43.6640625" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="27.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="26.44140625" customWidth="1"/>
     <col min="6" max="6" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="31.88671875" customWidth="1"/>
     <col min="8" max="8" width="75.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>166</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -844,1932 +634,1064 @@
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="6">
+        <v>45658</v>
+      </c>
+      <c r="J2" s="6">
+        <v>47484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="6">
+        <v>45672</v>
+      </c>
+      <c r="J3" s="6">
+        <v>47498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="6">
+        <v>45689</v>
+      </c>
+      <c r="J4" s="6">
+        <v>47515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6">
+        <v>45698</v>
+      </c>
+      <c r="J5" s="6">
+        <v>47524</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="6">
+        <v>45708</v>
+      </c>
+      <c r="J6" s="6">
+        <v>47534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="6">
+        <v>45717</v>
+      </c>
+      <c r="J7" s="6">
+        <v>47543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="6">
+        <v>45721</v>
+      </c>
+      <c r="J8" s="6">
+        <v>47547</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="6">
+        <v>45726</v>
+      </c>
+      <c r="J9" s="6">
+        <v>47552</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="6">
+        <v>45736</v>
+      </c>
+      <c r="J10" s="6">
+        <v>47562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="6">
+        <v>45748</v>
+      </c>
+      <c r="J11" s="6">
+        <v>47574</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="6">
+        <v>45757</v>
+      </c>
+      <c r="J12" s="6">
+        <v>47583</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="6">
+        <v>45767</v>
+      </c>
+      <c r="J13" s="6">
+        <v>47593</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="6">
+        <v>45778</v>
+      </c>
+      <c r="J14" s="6">
+        <v>47604</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="6">
+        <v>45792</v>
+      </c>
+      <c r="J15" s="6">
+        <v>47618</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="H16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="6">
+        <v>45802</v>
+      </c>
+      <c r="J16" s="6">
+        <v>47628</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J2" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="F17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="6">
+        <v>45809</v>
+      </c>
+      <c r="J17" s="6">
+        <v>47635</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="6">
+        <v>45823</v>
+      </c>
+      <c r="J18" s="6">
+        <v>47649</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="6">
+        <v>45828</v>
+      </c>
+      <c r="J19" s="6">
+        <v>47654</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="6">
+        <v>45839</v>
+      </c>
+      <c r="J20" s="6">
+        <v>47665</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J3" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="H21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="6">
+        <v>45848</v>
+      </c>
+      <c r="J21" s="6">
+        <v>47674</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" s="6">
+        <v>45870</v>
+      </c>
+      <c r="J22" s="6">
+        <v>47696</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="6">
+        <v>45884</v>
+      </c>
+      <c r="J23" s="6">
+        <v>47710</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="6">
+        <v>45894</v>
+      </c>
+      <c r="J24" s="6">
+        <v>47720</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="6">
+        <v>45901</v>
+      </c>
+      <c r="J25" s="6">
+        <v>47727</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="6">
+        <v>45915</v>
+      </c>
+      <c r="J26" s="6">
+        <v>47741</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="6">
+        <v>45925</v>
+      </c>
+      <c r="J27" s="6">
+        <v>47751</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J4" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="F28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J5" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="H28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I28" s="6">
+        <v>45931</v>
+      </c>
+      <c r="J28" s="6">
+        <v>47757</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="H29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="6">
+        <v>45945</v>
+      </c>
+      <c r="J29" s="6">
+        <v>47771</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J6" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J7" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J8" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J9" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J10" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J11" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J12" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J13" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J14" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J15" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J16" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J17" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J18" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" t="s">
-        <v>55</v>
-      </c>
-      <c r="I19" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J19" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" t="s">
-        <v>59</v>
-      </c>
-      <c r="I20" s="3">
-        <v>45658</v>
-      </c>
-      <c r="J20" s="3">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="3">
-        <v>45809</v>
-      </c>
-      <c r="J21" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J22" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" t="s">
-        <v>65</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" t="s">
-        <v>67</v>
-      </c>
-      <c r="I23" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J23" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" t="s">
-        <v>71</v>
-      </c>
-      <c r="I24" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J24" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
-        <v>72</v>
-      </c>
-      <c r="I25" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J25" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" t="s">
-        <v>76</v>
-      </c>
-      <c r="I26" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J26" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" t="s">
-        <v>77</v>
-      </c>
-      <c r="I27" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J27" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" t="s">
-        <v>81</v>
-      </c>
-      <c r="I28" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J28" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" t="s">
-        <v>80</v>
-      </c>
-      <c r="E29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" t="s">
-        <v>82</v>
-      </c>
-      <c r="I29" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J29" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" t="s">
-        <v>86</v>
-      </c>
-      <c r="I30" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J30" s="3">
-        <v>46054</v>
+      <c r="H30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="6">
+        <v>45955</v>
+      </c>
+      <c r="J30" s="6">
+        <v>47781</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" t="s">
-        <v>87</v>
-      </c>
-      <c r="I31" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J31" s="3">
-        <v>46204</v>
-      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
     </row>
     <row r="32" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" t="s">
-        <v>65</v>
-      </c>
-      <c r="F32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J32" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" t="s">
-        <v>92</v>
-      </c>
-      <c r="I33" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J33" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>93</v>
-      </c>
-      <c r="B34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" t="s">
-        <v>96</v>
-      </c>
-      <c r="I34" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J34" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F35" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" t="s">
-        <v>97</v>
-      </c>
-      <c r="I35" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J35" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E36" t="s">
-        <v>65</v>
-      </c>
-      <c r="F36" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" t="s">
-        <v>12</v>
-      </c>
-      <c r="H36" t="s">
-        <v>101</v>
-      </c>
-      <c r="I36" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J36" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" t="s">
-        <v>100</v>
-      </c>
-      <c r="E37" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" t="s">
-        <v>102</v>
-      </c>
-      <c r="I37" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J37" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>103</v>
-      </c>
-      <c r="B38" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" t="s">
-        <v>12</v>
-      </c>
-      <c r="H38" t="s">
-        <v>106</v>
-      </c>
-      <c r="I38" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J38" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>103</v>
-      </c>
-      <c r="B39" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" t="s">
-        <v>65</v>
-      </c>
-      <c r="F39" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" t="s">
-        <v>107</v>
-      </c>
-      <c r="I39" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J39" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" t="s">
-        <v>110</v>
-      </c>
-      <c r="E40" t="s">
-        <v>65</v>
-      </c>
-      <c r="F40" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" t="s">
-        <v>111</v>
-      </c>
-      <c r="I40" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J40" s="3">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>108</v>
-      </c>
-      <c r="B41" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" t="s">
-        <v>110</v>
-      </c>
-      <c r="E41" t="s">
-        <v>65</v>
-      </c>
-      <c r="F41" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" t="s">
-        <v>112</v>
-      </c>
-      <c r="I41" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J41" s="3">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>113</v>
-      </c>
-      <c r="B42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" t="s">
-        <v>117</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>118</v>
-      </c>
-      <c r="H42" t="s">
-        <v>119</v>
-      </c>
-      <c r="I42" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J42" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" t="s">
-        <v>116</v>
-      </c>
-      <c r="E43" t="s">
-        <v>117</v>
-      </c>
-      <c r="F43" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" t="s">
-        <v>120</v>
-      </c>
-      <c r="I43" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J43" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>113</v>
-      </c>
-      <c r="B44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" t="s">
-        <v>121</v>
-      </c>
-      <c r="D44" t="s">
-        <v>122</v>
-      </c>
-      <c r="E44" t="s">
-        <v>117</v>
-      </c>
-      <c r="F44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" t="s">
-        <v>123</v>
-      </c>
-      <c r="I44" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J44" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>113</v>
-      </c>
-      <c r="B45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E45" t="s">
-        <v>117</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" t="s">
-        <v>124</v>
-      </c>
-      <c r="I45" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J45" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C46" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" t="s">
-        <v>126</v>
-      </c>
-      <c r="E46" t="s">
-        <v>117</v>
-      </c>
-      <c r="F46" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>118</v>
-      </c>
-      <c r="H46" t="s">
-        <v>127</v>
-      </c>
-      <c r="I46" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J46" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47" t="s">
-        <v>125</v>
-      </c>
-      <c r="D47" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" t="s">
-        <v>117</v>
-      </c>
-      <c r="F47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" t="s">
-        <v>129</v>
-      </c>
-      <c r="I47" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J47" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>130</v>
-      </c>
-      <c r="B48" t="s">
-        <v>114</v>
-      </c>
-      <c r="C48" t="s">
-        <v>131</v>
-      </c>
-      <c r="D48" t="s">
-        <v>132</v>
-      </c>
-      <c r="E48" t="s">
-        <v>117</v>
-      </c>
-      <c r="F48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>118</v>
-      </c>
-      <c r="H48" t="s">
-        <v>133</v>
-      </c>
-      <c r="I48" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J48" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>130</v>
-      </c>
-      <c r="B49" t="s">
-        <v>114</v>
-      </c>
-      <c r="C49" t="s">
-        <v>131</v>
-      </c>
-      <c r="D49" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" t="s">
-        <v>117</v>
-      </c>
-      <c r="F49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" t="s">
-        <v>134</v>
-      </c>
-      <c r="I49" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J49" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>135</v>
-      </c>
-      <c r="B50" t="s">
-        <v>114</v>
-      </c>
-      <c r="C50" t="s">
-        <v>136</v>
-      </c>
-      <c r="D50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E50" t="s">
-        <v>117</v>
-      </c>
-      <c r="F50" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>118</v>
-      </c>
-      <c r="H50" t="s">
-        <v>138</v>
-      </c>
-      <c r="I50" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J50" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>135</v>
-      </c>
-      <c r="B51" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" t="s">
-        <v>136</v>
-      </c>
-      <c r="D51" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" t="s">
-        <v>117</v>
-      </c>
-      <c r="F51" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" t="s">
-        <v>139</v>
-      </c>
-      <c r="I51" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J51" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>140</v>
-      </c>
-      <c r="B52" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" t="s">
-        <v>142</v>
-      </c>
-      <c r="E52" t="s">
-        <v>117</v>
-      </c>
-      <c r="F52" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" t="s">
-        <v>118</v>
-      </c>
-      <c r="H52" t="s">
-        <v>143</v>
-      </c>
-      <c r="I52" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J52" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>140</v>
-      </c>
-      <c r="B53" t="s">
-        <v>114</v>
-      </c>
-      <c r="C53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D53" t="s">
-        <v>142</v>
-      </c>
-      <c r="E53" t="s">
-        <v>117</v>
-      </c>
-      <c r="F53" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" t="s">
-        <v>144</v>
-      </c>
-      <c r="I53" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J53" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>145</v>
-      </c>
-      <c r="B54" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" t="s">
-        <v>146</v>
-      </c>
-      <c r="D54" t="s">
-        <v>147</v>
-      </c>
-      <c r="E54" t="s">
-        <v>117</v>
-      </c>
-      <c r="F54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" t="s">
-        <v>118</v>
-      </c>
-      <c r="H54" t="s">
-        <v>148</v>
-      </c>
-      <c r="I54" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J54" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>145</v>
-      </c>
-      <c r="B55" t="s">
-        <v>114</v>
-      </c>
-      <c r="C55" t="s">
-        <v>146</v>
-      </c>
-      <c r="D55" t="s">
-        <v>147</v>
-      </c>
-      <c r="E55" t="s">
-        <v>117</v>
-      </c>
-      <c r="F55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s">
-        <v>149</v>
-      </c>
-      <c r="I55" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J55" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>150</v>
-      </c>
-      <c r="B56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" t="s">
-        <v>151</v>
-      </c>
-      <c r="D56" t="s">
-        <v>152</v>
-      </c>
-      <c r="E56" t="s">
-        <v>117</v>
-      </c>
-      <c r="F56" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>118</v>
-      </c>
-      <c r="H56" t="s">
-        <v>153</v>
-      </c>
-      <c r="I56" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J56" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>150</v>
-      </c>
-      <c r="B57" t="s">
-        <v>114</v>
-      </c>
-      <c r="C57" t="s">
-        <v>151</v>
-      </c>
-      <c r="D57" t="s">
-        <v>152</v>
-      </c>
-      <c r="E57" t="s">
-        <v>117</v>
-      </c>
-      <c r="F57" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" t="s">
-        <v>154</v>
-      </c>
-      <c r="I57" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J57" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>155</v>
-      </c>
-      <c r="B58" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" t="s">
-        <v>156</v>
-      </c>
-      <c r="D58" t="s">
-        <v>157</v>
-      </c>
-      <c r="E58" t="s">
-        <v>117</v>
-      </c>
-      <c r="F58" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" t="s">
-        <v>118</v>
-      </c>
-      <c r="H58" t="s">
-        <v>158</v>
-      </c>
-      <c r="I58" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J58" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>155</v>
-      </c>
-      <c r="B59" t="s">
-        <v>114</v>
-      </c>
-      <c r="C59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" t="s">
-        <v>157</v>
-      </c>
-      <c r="E59" t="s">
-        <v>117</v>
-      </c>
-      <c r="F59" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" t="s">
-        <v>159</v>
-      </c>
-      <c r="I59" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J59" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>160</v>
-      </c>
-      <c r="B60" t="s">
-        <v>114</v>
-      </c>
-      <c r="C60" t="s">
-        <v>161</v>
-      </c>
-      <c r="D60" t="s">
-        <v>162</v>
-      </c>
-      <c r="E60" t="s">
-        <v>117</v>
-      </c>
-      <c r="F60" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" t="s">
-        <v>118</v>
-      </c>
-      <c r="H60" t="s">
-        <v>163</v>
-      </c>
-      <c r="I60" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J60" s="3">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>160</v>
-      </c>
-      <c r="B61" t="s">
-        <v>114</v>
-      </c>
-      <c r="C61" t="s">
-        <v>161</v>
-      </c>
-      <c r="D61" t="s">
-        <v>162</v>
-      </c>
-      <c r="E61" t="s">
-        <v>117</v>
-      </c>
-      <c r="F61" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" t="s">
-        <v>164</v>
-      </c>
-      <c r="I61" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J61" s="3">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="H64" s="2"/>
     </row>
     <row r="65" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
@@ -5579,6 +4501,974 @@
     </row>
     <row r="1000" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="H1000" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D25B68F-C6BE-44E7-9509-9DF11FBE791B}">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="6">
+        <v>45658</v>
+      </c>
+      <c r="J2" s="6">
+        <v>47484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="6">
+        <v>45672</v>
+      </c>
+      <c r="J3" s="6">
+        <v>47498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="6">
+        <v>45689</v>
+      </c>
+      <c r="J4" s="6">
+        <v>47515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6">
+        <v>45698</v>
+      </c>
+      <c r="J5" s="6">
+        <v>47524</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="6">
+        <v>45708</v>
+      </c>
+      <c r="J6" s="6">
+        <v>47534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="6">
+        <v>45717</v>
+      </c>
+      <c r="J7" s="6">
+        <v>47543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="6">
+        <v>45721</v>
+      </c>
+      <c r="J8" s="6">
+        <v>47547</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="6">
+        <v>45726</v>
+      </c>
+      <c r="J9" s="6">
+        <v>47552</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="6">
+        <v>45736</v>
+      </c>
+      <c r="J10" s="6">
+        <v>47562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="6">
+        <v>45748</v>
+      </c>
+      <c r="J11" s="6">
+        <v>47574</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="6">
+        <v>45757</v>
+      </c>
+      <c r="J12" s="6">
+        <v>47583</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="6">
+        <v>45767</v>
+      </c>
+      <c r="J13" s="6">
+        <v>47593</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="6">
+        <v>45778</v>
+      </c>
+      <c r="J14" s="6">
+        <v>47604</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="6">
+        <v>45792</v>
+      </c>
+      <c r="J15" s="6">
+        <v>47618</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="6">
+        <v>45802</v>
+      </c>
+      <c r="J16" s="6">
+        <v>47628</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="6">
+        <v>45809</v>
+      </c>
+      <c r="J17" s="6">
+        <v>47635</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="6">
+        <v>45823</v>
+      </c>
+      <c r="J18" s="6">
+        <v>47649</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="6">
+        <v>45828</v>
+      </c>
+      <c r="J19" s="6">
+        <v>47654</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="6">
+        <v>45839</v>
+      </c>
+      <c r="J20" s="6">
+        <v>47665</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="6">
+        <v>45848</v>
+      </c>
+      <c r="J21" s="6">
+        <v>47674</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" s="6">
+        <v>45870</v>
+      </c>
+      <c r="J22" s="6">
+        <v>47696</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="6">
+        <v>45884</v>
+      </c>
+      <c r="J23" s="6">
+        <v>47710</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="6">
+        <v>45894</v>
+      </c>
+      <c r="J24" s="6">
+        <v>47720</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="6">
+        <v>45901</v>
+      </c>
+      <c r="J25" s="6">
+        <v>47727</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="6">
+        <v>45915</v>
+      </c>
+      <c r="J26" s="6">
+        <v>47741</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="6">
+        <v>45925</v>
+      </c>
+      <c r="J27" s="6">
+        <v>47751</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I28" s="6">
+        <v>45931</v>
+      </c>
+      <c r="J28" s="6">
+        <v>47757</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="6">
+        <v>45945</v>
+      </c>
+      <c r="J29" s="6">
+        <v>47771</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="6">
+        <v>45955</v>
+      </c>
+      <c r="J30" s="6">
+        <v>47781</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
